--- a/docs/design/ACSMS-SCR-029/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_増減通知（日本農業新聞）出力画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-029/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_増減通知（日本農業新聞）出力画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1363,20 +1363,144 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="inlineStr"/>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026/07/02</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>減部数を「▲」なしの数値表示に変更（顧客要望）。</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="18" t="inlineStr"/>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="20" t="inlineStr">
+        <is>
+          <t>実装との差分補完：カテゴリ6を新設し1件追加（TC-048）。集計対象を紙版のみに限定したこと（顧客要件2026-08 / #56410・API設計書 v1.4）。本帳票も部数の増減を伝えるもので電子版・併読は配達を伴わないため対象外。従来の「電子版は承認済のみ集計」条件は紙版限定に包含されるため廃止された。SCR-028 と同方針だが条件は各画面が個別に持つため、両帳票で対象購読者が一致することの確認をステップに含めた。なお本画面は出力条件に販売店の入力欄が無いためダミー販売店の表示制御（#56597）は対象外（API設計書 v1.5 に「コード変更なし」として記録済み）</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="11" t="n"/>
+      <c r="W4" s="19" t="inlineStr"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="11" t="n"/>
+      <c r="AC4" s="19" t="inlineStr"/>
+      <c r="AD4" s="10" t="n"/>
+      <c r="AE4" s="10" t="n"/>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="24">
+    <mergeCell ref="O3:V3"/>
+    <mergeCell ref="W1:AB1"/>
+    <mergeCell ref="W3:AB3"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="AC4:AH4"/>
+    <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="O1:V1"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC2:AH2"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="W4:AB4"/>
     <mergeCell ref="B1:E1"/>
-    <mergeCell ref="AC2:AH2"/>
-    <mergeCell ref="AC1:AH1"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
-    <mergeCell ref="W1:AB1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="O1:V1"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6239,7 +6363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ59"/>
+  <dimension ref="A1:BQ65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -10854,7 +10978,7 @@
       <c r="BP37" s="10" t="n"/>
       <c r="BQ37" s="11" t="n"/>
     </row>
-    <row r="38" ht="304" customHeight="1">
+    <row r="38" ht="320" customHeight="1">
       <c r="A38" s="44" t="n">
         <v>23</v>
       </c>
@@ -10978,7 +11102,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・減部数が `dokusya_busu &lt; 現在部数` のとき `現在部数 - dokusya_busu`、それ以外は0で、帳票では「▲」付きで表示されること
+            <t xml:space="preserve">・減部数が `dokusya_busu &lt; 現在部数` のとき `現在部数 - dokusya_busu`、それ以外は0で、帳票では数値のまま（マイナス符号「▲」なし）で表示されること
 </t>
           </r>
           <r>
@@ -11046,14 +11170,14 @@
       </c>
       <c r="B39" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-024</t>
+          <t>ACSMS-TC-029-044</t>
         </is>
       </c>
       <c r="C39" s="10" t="n"/>
       <c r="D39" s="11" t="n"/>
       <c r="E39" s="46" t="inlineStr">
         <is>
-          <t>委託欄の表示</t>
+          <t>同日複数履歴の累計（1→3→5 を 現在1/新5/増4）</t>
         </is>
       </c>
       <c r="F39" s="10" t="n"/>
@@ -11063,7 +11187,7 @@
       <c r="J39" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・委託区分が日農委託・振込・その他の販売店が存在する</t>
+・同一購読者が同じ適用日に部数を 1→3→5 と複数回変更した履歴が存在する（同日2レコード以上）</t>
         </is>
       </c>
       <c r="K39" s="10" t="n"/>
@@ -11088,7 +11212,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">適用日を入力して「レポートプレビュー」を実行する
+            <t xml:space="preserve">当該適用日を入力して「レポートプレビュー」を実行する
 </t>
           </r>
           <r>
@@ -11105,7 +11229,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>明細行の委託欄を確認する</t>
+            <t>該当販売店の明細行を確認する</t>
           </r>
         </is>
       </c>
@@ -11148,15 +11272,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・委託区分が日農委託（`itaku_kubun=2`）の販売店は委託欄に「委託」が表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・委託区分が振込（1）・その他（9）の販売店は委託欄が空欄で表示されること</t>
+            <t xml:space="preserve">・該当購読者の変動が **1行**（2行ではなく累計）で計上されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・現在部数 **1**、新部数 **5**、増部数 **4**、減部数 **0** であること</t>
           </r>
         </is>
       </c>
@@ -11210,20 +11334,20 @@
       <c r="BP39" s="10" t="n"/>
       <c r="BQ39" s="11" t="n"/>
     </row>
-    <row r="40" ht="144" customHeight="1">
+    <row r="40" ht="112" customHeight="1">
       <c r="A40" s="44" t="n">
         <v>25</v>
       </c>
       <c r="B40" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-025</t>
+          <t>ACSMS-TC-029-045</t>
         </is>
       </c>
       <c r="C40" s="10" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="46" t="inlineStr">
         <is>
-          <t>免税販売店の表示</t>
+          <t>解約（…→0）が減部数に反映</t>
         </is>
       </c>
       <c r="F40" s="10" t="n"/>
@@ -11233,7 +11357,7 @@
       <c r="J40" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・適格請求書発行事業者番号が空の販売店が存在する</t>
+・当該適用日に解約（購読部数 2→0）した購読者が存在する</t>
         </is>
       </c>
       <c r="K40" s="10" t="n"/>
@@ -11258,7 +11382,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">適用日を入力して「レポートプレビュー」を実行する
+            <t xml:space="preserve">当該適用日を入力して「レポートプレビュー」を実行する
 </t>
           </r>
           <r>
@@ -11275,7 +11399,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>明細行の販売店名を確認する</t>
+            <t>該当販売店の明細行を確認する</t>
           </r>
         </is>
       </c>
@@ -11318,7 +11442,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>適格請求書発行事業者番号（`torihikisaki_no`）が空の販売店は、販売店名の先頭に「（免）」が付与されて表示されること</t>
+            <t>・現在部数 **2**、減部数 **2**、新部数 **0**、増部数 **0** であること</t>
           </r>
         </is>
       </c>
@@ -11372,20 +11496,20 @@
       <c r="BP40" s="10" t="n"/>
       <c r="BQ40" s="11" t="n"/>
     </row>
-    <row r="41" ht="128" customHeight="1">
+    <row r="41" ht="160" customHeight="1">
       <c r="A41" s="44" t="n">
         <v>26</v>
       </c>
       <c r="B41" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-026</t>
+          <t>ACSMS-TC-029-046</t>
         </is>
       </c>
       <c r="C41" s="10" t="n"/>
       <c r="D41" s="11" t="n"/>
       <c r="E41" s="46" t="inlineStr">
         <is>
-          <t>前回出力との差異マーク</t>
+          <t>販売店変更（旧店に減 / 新店に増）</t>
         </is>
       </c>
       <c r="F41" s="10" t="n"/>
@@ -11395,7 +11519,7 @@
       <c r="J41" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・前回出力時点と値が異なる販売店が存在する</t>
+・当該適用日に販売店を A→B に変更した購読者が存在する（部数は不変 1→1）</t>
         </is>
       </c>
       <c r="K41" s="10" t="n"/>
@@ -11420,7 +11544,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">適用日を入力して「レポートプレビュー」を実行する
+            <t xml:space="preserve">当該適用日を入力して「レポートプレビュー」を実行する
 </t>
           </r>
           <r>
@@ -11437,7 +11561,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>明細行の差異マークを確認する</t>
+            <t>旧販売店A・新販売店B の明細行を確認する</t>
           </r>
         </is>
       </c>
@@ -11480,7 +11604,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>前回出力時点の値と差がある行は差異マーク（`diff_mark=true`、帳票では「◆」）が付与されて表示されること</t>
+            <t xml:space="preserve">・旧販売店A：現在部数 **1** / 減部数 **1** / 新部数 **0** で表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・新販売店B：現在部数 **0** / 増部数 **1** / 新部数 **1** で表示されること</t>
           </r>
         </is>
       </c>
@@ -11526,7 +11658,11 @@
       <c r="BH41" s="45" t="inlineStr"/>
       <c r="BI41" s="10" t="n"/>
       <c r="BJ41" s="11" t="n"/>
-      <c r="BK41" s="46" t="inlineStr"/>
+      <c r="BK41" s="46" t="inlineStr">
+        <is>
+          <t>旧店の管理支店は履歴に保持されないため、暫定的に当日最終レコードの管理支店に計上する。</t>
+        </is>
+      </c>
       <c r="BL41" s="10" t="n"/>
       <c r="BM41" s="10" t="n"/>
       <c r="BN41" s="10" t="n"/>
@@ -11534,20 +11670,20 @@
       <c r="BP41" s="10" t="n"/>
       <c r="BQ41" s="11" t="n"/>
     </row>
-    <row r="42" ht="80" customHeight="1">
+    <row r="42" ht="160" customHeight="1">
       <c r="A42" s="44" t="n">
         <v>27</v>
       </c>
       <c r="B42" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-027</t>
+          <t>ACSMS-TC-029-024</t>
         </is>
       </c>
       <c r="C42" s="10" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="46" t="inlineStr">
         <is>
-          <t>現在部数0かつ新部数0のレコード除外</t>
+          <t>委託欄の表示</t>
         </is>
       </c>
       <c r="F42" s="10" t="n"/>
@@ -11557,7 +11693,7 @@
       <c r="J42" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・現在部数=0 かつ 新部数=0 の履歴が存在する</t>
+・委託区分が日農委託・振込・その他の販売店が存在する</t>
         </is>
       </c>
       <c r="K42" s="10" t="n"/>
@@ -11582,7 +11718,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>適用日を入力して「レポートプレビュー」を実行する</t>
+            <t xml:space="preserve">適用日を入力して「レポートプレビュー」を実行する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>明細行の委託欄を確認する</t>
           </r>
         </is>
       </c>
@@ -11608,7 +11761,32 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>現在部数=0 かつ 新部数=0（`COALESCE(zenkai_dokusya_busu,0)=0 AND dokusya_busu=0`）のレコードが表示されないこと</t>
+            <t xml:space="preserve">一覧が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・委託区分が日農委託（`itaku_kubun=2`）の販売店は委託欄に「委託」が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・委託区分が振込（1）・その他（9）の販売店は委託欄が空欄で表示されること</t>
           </r>
         </is>
       </c>
@@ -11662,20 +11840,20 @@
       <c r="BP42" s="10" t="n"/>
       <c r="BQ42" s="11" t="n"/>
     </row>
-    <row r="43" ht="64" customHeight="1">
+    <row r="43" ht="144" customHeight="1">
       <c r="A43" s="44" t="n">
         <v>28</v>
       </c>
       <c r="B43" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-028</t>
+          <t>ACSMS-TC-029-025</t>
         </is>
       </c>
       <c r="C43" s="10" t="n"/>
       <c r="D43" s="11" t="n"/>
       <c r="E43" s="46" t="inlineStr">
         <is>
-          <t>廃店の除外</t>
+          <t>免税販売店の表示</t>
         </is>
       </c>
       <c r="F43" s="10" t="n"/>
@@ -11685,7 +11863,7 @@
       <c r="J43" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・廃店（haiten_flg=true）・電子版ダミー販売店の履歴が存在する</t>
+・適格請求書発行事業者番号が空の販売店が存在する</t>
         </is>
       </c>
       <c r="K43" s="10" t="n"/>
@@ -11710,7 +11888,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>適用日を入力して「レポートプレビュー」を実行する</t>
+            <t xml:space="preserve">適用日を入力して「レポートプレビュー」を実行する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>明細行の販売店名を確認する</t>
           </r>
         </is>
       </c>
@@ -11736,7 +11931,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>廃店（haiten_flg=true）・電子版ダミー販売店に紐づくレコードが表示されないこと</t>
+            <t xml:space="preserve">一覧が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>適格請求書発行事業者番号（`torihikisaki_no`）が空の販売店は、販売店名の先頭に「（免）」が付与されて表示されること</t>
           </r>
         </is>
       </c>
@@ -11796,14 +12008,14 @@
       </c>
       <c r="B44" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-029</t>
+          <t>ACSMS-TC-029-026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n"/>
       <c r="D44" s="11" t="n"/>
       <c r="E44" s="46" t="inlineStr">
         <is>
-          <t>合計行の集計</t>
+          <t>前回出力との差異マーク</t>
         </is>
       </c>
       <c r="F44" s="10" t="n"/>
@@ -11813,7 +12025,7 @@
       <c r="J44" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・1管理支店に複数の販売店が存在する</t>
+・前回出力時点と値が異なる販売店が存在する</t>
         </is>
       </c>
       <c r="K44" s="10" t="n"/>
@@ -11855,7 +12067,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>合計行と明細行を照合する</t>
+            <t>明細行の差異マークを確認する</t>
           </r>
         </is>
       </c>
@@ -11898,7 +12110,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>合計行の現在部数・増部数・減部数・新部数が、当該管理支店内の各明細行の総和と一致すること</t>
+            <t>前回出力時点の値と差がある行は差異マーク（`diff_mark=true`、帳票では「◆」）が付与されて表示されること</t>
           </r>
         </is>
       </c>
@@ -11952,20 +12164,20 @@
       <c r="BP44" s="10" t="n"/>
       <c r="BQ44" s="11" t="n"/>
     </row>
-    <row r="45" ht="112" customHeight="1">
+    <row r="45" ht="80" customHeight="1">
       <c r="A45" s="44" t="n">
         <v>30</v>
       </c>
       <c r="B45" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-030</t>
+          <t>ACSMS-TC-029-027</t>
         </is>
       </c>
       <c r="C45" s="10" t="n"/>
       <c r="D45" s="11" t="n"/>
       <c r="E45" s="46" t="inlineStr">
         <is>
-          <t>管理支店コードのハイフン区切り表示</t>
+          <t>現在部数0かつ新部数0のレコード除外</t>
         </is>
       </c>
       <c r="F45" s="10" t="n"/>
@@ -11975,7 +12187,7 @@
       <c r="J45" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・10桁の管理支店コードを持つ管理支店が存在する</t>
+・現在部数=0 かつ 新部数=0 の履歴が存在する</t>
         </is>
       </c>
       <c r="K45" s="10" t="n"/>
@@ -12000,24 +12212,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">適用日を入力して「レポートプレビュー」を実行する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>帳票ヘッダの管理支店コード表示を確認する</t>
+            <t>適用日を入力して「レポートプレビュー」を実行する</t>
           </r>
         </is>
       </c>
@@ -12043,24 +12238,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">一覧が表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>管理支店コードが10桁を3-4-3でハイフン区切りで表示されること（例：1AA-3300-001）</t>
+            <t>現在部数=0 かつ 新部数=0（`COALESCE(zenkai_dokusya_busu,0)=0 AND dokusya_busu=0`）のレコードが表示されないこと</t>
           </r>
         </is>
       </c>
@@ -12114,20 +12292,20 @@
       <c r="BP45" s="10" t="n"/>
       <c r="BQ45" s="11" t="n"/>
     </row>
-    <row r="46" ht="128" customHeight="1">
+    <row r="46" ht="64" customHeight="1">
       <c r="A46" s="44" t="n">
         <v>31</v>
       </c>
       <c r="B46" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-031</t>
+          <t>ACSMS-TC-029-028</t>
         </is>
       </c>
       <c r="C46" s="10" t="n"/>
       <c r="D46" s="11" t="n"/>
       <c r="E46" s="46" t="inlineStr">
         <is>
-          <t>対象0件（プレビュー）</t>
+          <t>廃店の除外</t>
         </is>
       </c>
       <c r="F46" s="10" t="n"/>
@@ -12137,7 +12315,7 @@
       <c r="J46" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・指定した条件に対象データが存在しない</t>
+・廃店（haiten_flg=true）・電子版ダミー販売店の履歴が存在する</t>
         </is>
       </c>
       <c r="K46" s="10" t="n"/>
@@ -12162,7 +12340,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>対象が存在しない適用日・条件で「レポートプレビュー」を実行する</t>
+            <t>適用日を入力して「レポートプレビュー」を実行する</t>
           </r>
         </is>
       </c>
@@ -12188,15 +12366,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・HTTPステータスコード200が返却されること（`reports:[]`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・メッセージ「対象のデータが存在しません。」が表示されること（ACSMS-MSG-029-002、トーストではない）</t>
+            <t>廃店（haiten_flg=true）・電子版ダミー販売店に紐づくレコードが表示されないこと</t>
           </r>
         </is>
       </c>
@@ -12208,7 +12378,7 @@
       <c r="AD46" s="11" t="n"/>
       <c r="AE46" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF46" s="11" t="n"/>
@@ -12250,20 +12420,20 @@
       <c r="BP46" s="10" t="n"/>
       <c r="BQ46" s="11" t="n"/>
     </row>
-    <row r="47" ht="160" customHeight="1">
+    <row r="47" ht="128" customHeight="1">
       <c r="A47" s="44" t="n">
         <v>32</v>
       </c>
       <c r="B47" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-032</t>
+          <t>ACSMS-TC-029-029</t>
         </is>
       </c>
       <c r="C47" s="10" t="n"/>
       <c r="D47" s="11" t="n"/>
       <c r="E47" s="46" t="inlineStr">
         <is>
-          <t>電子帳票作成前の確認ダイアログ</t>
+          <t>合計行の集計</t>
         </is>
       </c>
       <c r="F47" s="10" t="n"/>
@@ -12273,7 +12443,7 @@
       <c r="J47" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・適用日に対象データが存在する</t>
+・1管理支店に複数の販売店が存在する</t>
         </is>
       </c>
       <c r="K47" s="10" t="n"/>
@@ -12298,7 +12468,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">適用日を入力して「電子帳票作成」ボタンをクリックする
+            <t xml:space="preserve">適用日を入力して「レポートプレビュー」を実行する
 </t>
           </r>
           <r>
@@ -12315,7 +12485,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>確認ダイアログで「いいえ」をクリックする</t>
+            <t>合計行と明細行を照合する</t>
           </r>
         </is>
       </c>
@@ -12341,7 +12511,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">確認メッセージが表示されること（メッセージ「増減通知を作成して日農担当者へメール送信を実行します。よろしいですか？」＝ACSMS-MSG-029-005）
+            <t xml:space="preserve">一覧が表示されること
 </t>
           </r>
           <r>
@@ -12358,7 +12528,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>処理が中止され、PDF生成・メール送信が実行されないこと</t>
+            <t>合計行の現在部数・増部数・減部数・新部数が、当該管理支店内の各明細行の総和と一致すること</t>
           </r>
         </is>
       </c>
@@ -12412,20 +12582,20 @@
       <c r="BP47" s="10" t="n"/>
       <c r="BQ47" s="11" t="n"/>
     </row>
-    <row r="48" ht="272" customHeight="1">
+    <row r="48" ht="112" customHeight="1">
       <c r="A48" s="44" t="n">
         <v>33</v>
       </c>
       <c r="B48" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-033</t>
+          <t>ACSMS-TC-029-030</t>
         </is>
       </c>
       <c r="C48" s="10" t="n"/>
       <c r="D48" s="11" t="n"/>
       <c r="E48" s="46" t="inlineStr">
         <is>
-          <t>電子帳票（PDF）出力・S3保存・メール通知（単一管理支店）</t>
+          <t>管理支店コードのハイフン区切り表示</t>
         </is>
       </c>
       <c r="F48" s="10" t="n"/>
@@ -12435,7 +12605,7 @@
       <c r="J48" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・対象管理支店が1件のみ該当する適用日・条件</t>
+・10桁の管理支店コードを持つ管理支店が存在する</t>
         </is>
       </c>
       <c r="K48" s="10" t="n"/>
@@ -12460,7 +12630,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>適用日・管理支店を選択して「電子帳票作成」を実行し、確認ダイアログで「はい」をクリックする</t>
+            <t xml:space="preserve">適用日を入力して「レポートプレビュー」を実行する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>帳票ヘッダの管理支店コード表示を確認する</t>
           </r>
         </is>
       </c>
@@ -12486,40 +12673,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・HTTPステータスコード200が返却されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・PDFファイルがダウンロードされること（`Content-Type: application/pdf`、ファイル名 `増減通知_{管理支店コード}_{適用日YYYYMMDD}.pdf`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・生成したPDFがS3に保存されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・日農担当者へ増減通知の作成完了メールが送信されること（件名プレフィックス `【AgriNews_ACSMS】`、本文に個人情報を含まないこと）</t>
+            <t xml:space="preserve">一覧が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>管理支店コードが10桁を3-4-3でハイフン区切りで表示されること（例：1AA-3300-001）</t>
           </r>
         </is>
       </c>
@@ -12573,20 +12744,20 @@
       <c r="BP48" s="10" t="n"/>
       <c r="BQ48" s="11" t="n"/>
     </row>
-    <row r="49" ht="432" customHeight="1">
+    <row r="49" ht="128" customHeight="1">
       <c r="A49" s="44" t="n">
         <v>34</v>
       </c>
       <c r="B49" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-034</t>
+          <t>ACSMS-TC-029-031</t>
         </is>
       </c>
       <c r="C49" s="10" t="n"/>
       <c r="D49" s="11" t="n"/>
       <c r="E49" s="46" t="inlineStr">
         <is>
-          <t>複数管理支店のZIP出力・履歴・操作ログ</t>
+          <t>対象0件（プレビュー）</t>
         </is>
       </c>
       <c r="F49" s="10" t="n"/>
@@ -12596,7 +12767,7 @@
       <c r="J49" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・対象管理支店が複数件該当する適用日・条件</t>
+・指定した条件に対象データが存在しない</t>
         </is>
       </c>
       <c r="K49" s="10" t="n"/>
@@ -12621,112 +12792,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">適用日・複数の管理支店を選択して「電子帳票作成」を実行し、確認ダイアログで「はい」をクリックする
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">DBで以下クエリを実行し、ダウンロード履歴と操作ログを確認
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">```sql
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT download_type, file_name, record_count, target_month
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_file_download
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">WHERE ja_id = 1
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ORDER BY download_datetime DESC;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT log_type, operation, result_status, target_table
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_log
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">WHERE ja_id = 1 AND gamen_name = '増減通知（日本農業新聞）出力画面 (ACSMS-SCR-029)'
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ORDER BY log_datetime DESC
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">LIMIT 1;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>```</t>
+            <t>対象が存在しない適用日・条件で「レポートプレビュー」を実行する</t>
           </r>
         </is>
       </c>
@@ -12752,32 +12818,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・各管理支店のPDFをまとめたZIPファイルがダウンロードされること（`Content-Type: application/zip`、ファイル名 `増減通知_{適用日YYYYMMDD}.zip`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・t_file_download にPDFファイルごとに履歴が登録されること（download_type=4、target_month に適用日の年月）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・t_log に監査ログが1件記録されること（log_type=1、operation=`EXPORT_PDF`、result_status=1、target_table=`t_file_download`）</t>
+            <t xml:space="preserve">・HTTPステータスコード200が返却されること（`reports:[]`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・メッセージ「対象のデータが存在しません。」が表示されること（ACSMS-MSG-029-002、トーストではない）</t>
           </r>
         </is>
       </c>
@@ -12789,7 +12838,7 @@
       <c r="AD49" s="11" t="n"/>
       <c r="AE49" s="45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AF49" s="11" t="n"/>
@@ -12831,20 +12880,20 @@
       <c r="BP49" s="10" t="n"/>
       <c r="BQ49" s="11" t="n"/>
     </row>
-    <row r="50" ht="224" customHeight="1">
+    <row r="50" ht="160" customHeight="1">
       <c r="A50" s="44" t="n">
         <v>35</v>
       </c>
       <c r="B50" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-035</t>
+          <t>ACSMS-TC-029-032</t>
         </is>
       </c>
       <c r="C50" s="10" t="n"/>
       <c r="D50" s="11" t="n"/>
       <c r="E50" s="46" t="inlineStr">
         <is>
-          <t>対象0件（電子帳票作成）</t>
+          <t>電子帳票作成前の確認ダイアログ</t>
         </is>
       </c>
       <c r="F50" s="10" t="n"/>
@@ -12854,7 +12903,7 @@
       <c r="J50" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・指定した条件に対象データが存在しない</t>
+・適用日に対象データが存在する</t>
         </is>
       </c>
       <c r="K50" s="10" t="n"/>
@@ -12879,7 +12928,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">対象が存在しない適用日・条件で「電子帳票作成」を実行し、確認ダイアログで「はい」をクリックする
+            <t xml:space="preserve">適用日を入力して「電子帳票作成」ボタンをクリックする
 </t>
           </r>
           <r>
@@ -12896,7 +12945,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DBで t_file_download の登録件数を確認する</t>
+            <t>確認ダイアログで「いいえ」をクリックする</t>
           </r>
         </is>
       </c>
@@ -12922,23 +12971,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・HTTPステータスコード200が返却されること（`application/json` の `{ data: { reports: [] } }`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・PDF／ZIPファイルがダウンロードされないこと
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・メッセージ「対象のデータが存在しません。」が表示されること（ACSMS-MSG-029-002）
+            <t xml:space="preserve">確認メッセージが表示されること（メッセージ「増減通知を作成して日農担当者へメール送信を実行します。よろしいですか？」＝ACSMS-MSG-029-005）
 </t>
           </r>
           <r>
@@ -12955,7 +12988,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>t_file_download にレコードが登録されないこと</t>
+            <t>処理が中止され、PDF生成・メール送信が実行されないこと</t>
           </r>
         </is>
       </c>
@@ -12967,7 +13000,7 @@
       <c r="AD50" s="11" t="n"/>
       <c r="AE50" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF50" s="11" t="n"/>
@@ -13009,20 +13042,20 @@
       <c r="BP50" s="10" t="n"/>
       <c r="BQ50" s="11" t="n"/>
     </row>
-    <row r="51" ht="256" customHeight="1">
+    <row r="51" ht="272" customHeight="1">
       <c r="A51" s="44" t="n">
         <v>36</v>
       </c>
       <c r="B51" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-036</t>
+          <t>ACSMS-TC-029-033</t>
         </is>
       </c>
       <c r="C51" s="10" t="n"/>
       <c r="D51" s="11" t="n"/>
       <c r="E51" s="46" t="inlineStr">
         <is>
-          <t>トランザクション ロールバック</t>
+          <t>電子帳票（PDF）出力・S3保存・メール通知（単一管理支店）</t>
         </is>
       </c>
       <c r="F51" s="10" t="n"/>
@@ -13032,7 +13065,7 @@
       <c r="J51" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・ダウンロード履歴登録時にDBエラーを発生させる準備ができている</t>
+・対象管理支店が1件のみ該当する適用日・条件</t>
         </is>
       </c>
       <c r="K51" s="10" t="n"/>
@@ -13057,24 +13090,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「電子帳票作成」を実行する（DB登録の途中でエラーを注入する）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>DBで t_file_download・t_log の状態を確認</t>
+            <t>適用日・管理支店を選択して「電子帳票作成」を実行し、確認ダイアログで「はい」をクリックする</t>
           </r>
         </is>
       </c>
@@ -13100,32 +13116,40 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード500が返却されること（`error_code: INTERNAL_SERVER_ERROR`、メッセージ `システムエラーが発生しました。しばらくしてから再度お試しください。`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・t_file_download・t_log（log_type=1）のいずれも登録されないこと（ロールバックされること）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・t_log にエラーログが1件記録されること（log_type=3、result_status=2）</t>
+            <t xml:space="preserve">・HTTPステータスコード200が返却されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・PDFファイルがダウンロードされること（`Content-Type: application/pdf`、ファイル名 `増減通知_{適用日YYYYMMDD}.pdf`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・生成したPDFがS3に保存されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・日農担当者へ増減通知の作成完了メールが送信されること（件名プレフィックス `【AgriNews_ACSMS】`、本文に個人情報を含まないこと）</t>
           </r>
         </is>
       </c>
@@ -13137,7 +13161,7 @@
       <c r="AD51" s="11" t="n"/>
       <c r="AE51" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF51" s="11" t="n"/>
@@ -13171,12 +13195,7 @@
       <c r="BH51" s="45" t="inlineStr"/>
       <c r="BI51" s="10" t="n"/>
       <c r="BJ51" s="11" t="n"/>
-      <c r="BK51" s="46" t="inlineStr">
-        <is>
-          <t>(なし)
----</t>
-        </is>
-      </c>
+      <c r="BK51" s="46" t="inlineStr"/>
       <c r="BL51" s="10" t="n"/>
       <c r="BM51" s="10" t="n"/>
       <c r="BN51" s="10" t="n"/>
@@ -13184,74 +13203,265 @@
       <c r="BP51" s="10" t="n"/>
       <c r="BQ51" s="11" t="n"/>
     </row>
-    <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="32" t="inlineStr">
-        <is>
-          <t>カテゴリ5: 共通エラーハンドリング（Common Error Handling）</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="n"/>
+    <row r="52" ht="432" customHeight="1">
+      <c r="A52" s="44" t="n">
+        <v>37</v>
+      </c>
+      <c r="B52" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-029-034</t>
+        </is>
+      </c>
       <c r="C52" s="10" t="n"/>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="46" t="inlineStr">
+        <is>
+          <t>複数管理支店を1つのPDFにまとめて出力・履歴・操作ログ</t>
+        </is>
+      </c>
       <c r="F52" s="10" t="n"/>
       <c r="G52" s="10" t="n"/>
       <c r="H52" s="10" t="n"/>
-      <c r="I52" s="10" t="n"/>
-      <c r="J52" s="10" t="n"/>
+      <c r="I52" s="11" t="n"/>
+      <c r="J52" s="46" t="inlineStr">
+        <is>
+          <t>・CHUOKAI でログイン済み
+・対象管理支店が複数件該当する適用日・条件</t>
+        </is>
+      </c>
       <c r="K52" s="10" t="n"/>
       <c r="L52" s="10" t="n"/>
       <c r="M52" s="10" t="n"/>
       <c r="N52" s="10" t="n"/>
       <c r="O52" s="10" t="n"/>
-      <c r="P52" s="10" t="n"/>
-      <c r="Q52" s="10" t="n"/>
+      <c r="P52" s="11" t="n"/>
+      <c r="Q52" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">適用日・複数の管理支店を選択して「電子帳票作成」を実行し、確認ダイアログで「はい」をクリックする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DBで以下クエリを実行し、ダウンロード履歴と操作ログを確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT download_type, file_name, record_count, target_month
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_file_download
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">WHERE ja_id = 1
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ORDER BY download_datetime DESC;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT log_type, operation, result_status, target_table
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_log
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">WHERE ja_id = 1 AND gamen_name = '増減通知（日本農業新聞）出力画面 (ACSMS-SCR-029)'
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ORDER BY log_datetime DESC
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">LIMIT 1;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>```</t>
+          </r>
+        </is>
+      </c>
       <c r="R52" s="10" t="n"/>
       <c r="S52" s="10" t="n"/>
       <c r="T52" s="10" t="n"/>
       <c r="U52" s="10" t="n"/>
       <c r="V52" s="10" t="n"/>
-      <c r="W52" s="10" t="n"/>
-      <c r="X52" s="10" t="n"/>
+      <c r="W52" s="11" t="n"/>
+      <c r="X52" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・全管理支店を**プレビューと同じ改ページ（15行/ページ）でまとめた1つのPDF**がダウンロードされること（`Content-Type: application/pdf`、ファイル名 `増減通知_{適用日YYYYMMDD}.pdf`、ZIPではない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・管理支店がページをまたぐ／1ページに複数管理支店が載る場合でも、PDF の n ページ目 = プレビューの n ページ目であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・t_file_download に履歴が**1件**登録されること（download_type=4、file_name=`増減通知_{YYYYMMDD}.pdf`、record_count=対象レコード総数、target_month に適用日の年月）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・t_log に監査ログが1件記録されること（log_type=1、operation=`EXPORT_PDF`、result_status=1、target_table=`t_file_download`）</t>
+          </r>
+        </is>
+      </c>
       <c r="Y52" s="10" t="n"/>
       <c r="Z52" s="10" t="n"/>
       <c r="AA52" s="10" t="n"/>
       <c r="AB52" s="10" t="n"/>
       <c r="AC52" s="10" t="n"/>
-      <c r="AD52" s="10" t="n"/>
-      <c r="AE52" s="10" t="n"/>
-      <c r="AF52" s="10" t="n"/>
-      <c r="AG52" s="10" t="n"/>
+      <c r="AD52" s="11" t="n"/>
+      <c r="AE52" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF52" s="11" t="n"/>
+      <c r="AG52" s="45" t="inlineStr"/>
       <c r="AH52" s="10" t="n"/>
-      <c r="AI52" s="10" t="n"/>
-      <c r="AJ52" s="10" t="n"/>
+      <c r="AI52" s="11" t="n"/>
+      <c r="AJ52" s="45" t="inlineStr"/>
       <c r="AK52" s="10" t="n"/>
-      <c r="AL52" s="10" t="n"/>
-      <c r="AM52" s="10" t="n"/>
+      <c r="AL52" s="11" t="n"/>
+      <c r="AM52" s="45" t="inlineStr"/>
       <c r="AN52" s="10" t="n"/>
-      <c r="AO52" s="10" t="n"/>
-      <c r="AP52" s="10" t="n"/>
+      <c r="AO52" s="11" t="n"/>
+      <c r="AP52" s="45" t="inlineStr"/>
       <c r="AQ52" s="10" t="n"/>
-      <c r="AR52" s="10" t="n"/>
-      <c r="AS52" s="10" t="n"/>
+      <c r="AR52" s="11" t="n"/>
+      <c r="AS52" s="45" t="inlineStr"/>
       <c r="AT52" s="10" t="n"/>
-      <c r="AU52" s="10" t="n"/>
-      <c r="AV52" s="10" t="n"/>
+      <c r="AU52" s="11" t="n"/>
+      <c r="AV52" s="45" t="inlineStr"/>
       <c r="AW52" s="10" t="n"/>
-      <c r="AX52" s="10" t="n"/>
-      <c r="AY52" s="10" t="n"/>
+      <c r="AX52" s="11" t="n"/>
+      <c r="AY52" s="45" t="inlineStr"/>
       <c r="AZ52" s="10" t="n"/>
-      <c r="BA52" s="10" t="n"/>
-      <c r="BB52" s="10" t="n"/>
+      <c r="BA52" s="11" t="n"/>
+      <c r="BB52" s="45" t="inlineStr"/>
       <c r="BC52" s="10" t="n"/>
-      <c r="BD52" s="10" t="n"/>
-      <c r="BE52" s="10" t="n"/>
+      <c r="BD52" s="11" t="n"/>
+      <c r="BE52" s="45" t="inlineStr"/>
       <c r="BF52" s="10" t="n"/>
-      <c r="BG52" s="10" t="n"/>
-      <c r="BH52" s="10" t="n"/>
+      <c r="BG52" s="11" t="n"/>
+      <c r="BH52" s="45" t="inlineStr"/>
       <c r="BI52" s="10" t="n"/>
-      <c r="BJ52" s="10" t="n"/>
-      <c r="BK52" s="10" t="n"/>
+      <c r="BJ52" s="11" t="n"/>
+      <c r="BK52" s="46" t="inlineStr"/>
       <c r="BL52" s="10" t="n"/>
       <c r="BM52" s="10" t="n"/>
       <c r="BN52" s="10" t="n"/>
@@ -13259,20 +13469,20 @@
       <c r="BP52" s="10" t="n"/>
       <c r="BQ52" s="11" t="n"/>
     </row>
-    <row r="53" ht="112" customHeight="1">
+    <row r="53" ht="224" customHeight="1">
       <c r="A53" s="44" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B53" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-037</t>
+          <t>ACSMS-TC-029-035</t>
         </is>
       </c>
       <c r="C53" s="10" t="n"/>
       <c r="D53" s="11" t="n"/>
       <c r="E53" s="46" t="inlineStr">
         <is>
-          <t>不正リクエストパラメータ（BAD_REQUEST）</t>
+          <t>対象0件（電子帳票作成）</t>
         </is>
       </c>
       <c r="F53" s="10" t="n"/>
@@ -13281,7 +13491,8 @@
       <c r="I53" s="11" t="n"/>
       <c r="J53" s="46" t="inlineStr">
         <is>
-          <t>・CHUOKAI でログイン済み</t>
+          <t>・CHUOKAI でログイン済み
+・指定した条件に対象データが存在しない</t>
         </is>
       </c>
       <c r="K53" s="10" t="n"/>
@@ -13306,7 +13517,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DevToolsのNetworkタブでGET「/api/v1/report/zougen-nichino/preview?tekiyo_date=2026-03-01&amp;kanri_shiten_id=abc」（数値項目に文字列）を送信</t>
+            <t xml:space="preserve">対象が存在しない適用日・条件で「電子帳票作成」を実行し、確認ダイアログで「はい」をクリックする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DBで t_file_download の登録件数を確認する</t>
           </r>
         </is>
       </c>
@@ -13332,7 +13560,40 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>HTTPステータスコード400が返却されること（`error_code: BAD_REQUEST`、メッセージ `リクエストパラメータが不正です。` または `error_code: VALIDATION_ERROR`）</t>
+            <t xml:space="preserve">・HTTPステータスコード200が返却されること（`application/json` の `{ data: { reports: [] } }`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・PDF／ZIPファイルがダウンロードされないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・メッセージ「対象のデータが存在しません。」が表示されること（ACSMS-MSG-029-002）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>t_file_download にレコードが登録されないこと</t>
           </r>
         </is>
       </c>
@@ -13386,20 +13647,20 @@
       <c r="BP53" s="10" t="n"/>
       <c r="BQ53" s="11" t="n"/>
     </row>
-    <row r="54" ht="208" customHeight="1">
+    <row r="54" ht="256" customHeight="1">
       <c r="A54" s="44" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B54" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-038</t>
+          <t>ACSMS-TC-029-036</t>
         </is>
       </c>
       <c r="C54" s="10" t="n"/>
       <c r="D54" s="11" t="n"/>
       <c r="E54" s="46" t="inlineStr">
         <is>
-          <t>セッション切れ（UNAUTHORIZED）</t>
+          <t>トランザクション ロールバック</t>
         </is>
       </c>
       <c r="F54" s="10" t="n"/>
@@ -13409,7 +13670,7 @@
       <c r="J54" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・管理ツールでセッションを強制失効させる準備ができている</t>
+・ダウンロード履歴登録時にDBエラーを発生させる準備ができている</t>
         </is>
       </c>
       <c r="K54" s="10" t="n"/>
@@ -13434,7 +13695,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">増減通知（日本農業新聞）出力画面を開いた状態でセッションを強制失効させる
+            <t xml:space="preserve">「電子帳票作成」を実行する（DB登録の途中でエラーを注入する）
 </t>
           </r>
           <r>
@@ -13451,7 +13712,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>「レポートプレビュー」ボタンをクリックする</t>
+            <t>DBで t_file_download・t_log の状態を確認</t>
           </r>
         </is>
       </c>
@@ -13477,7 +13738,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">画面が表示された状態であること
+            <t xml:space="preserve">HTTPステータスコード500が返却されること（`error_code: INTERNAL_SERVER_ERROR`、メッセージ `システムエラーが発生しました。しばらくしてから再度お試しください。`）
 </t>
           </r>
           <r>
@@ -13494,15 +13755,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・HTTPステータスコード401が返却されること（`error_code: UNAUTHORIZED`、メッセージ `セッションが切れました。再度ログインしてください。`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・「/login」へ遷移すること（クエリに `redirect` が付与されること）</t>
+            <t xml:space="preserve">・t_file_download・t_log（log_type=1）のいずれも登録されないこと（ロールバックされること）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・t_log にエラーログが1件記録されること（log_type=3、result_status=2）</t>
           </r>
         </is>
       </c>
@@ -13548,7 +13809,12 @@
       <c r="BH54" s="45" t="inlineStr"/>
       <c r="BI54" s="10" t="n"/>
       <c r="BJ54" s="11" t="n"/>
-      <c r="BK54" s="46" t="inlineStr"/>
+      <c r="BK54" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
       <c r="BL54" s="10" t="n"/>
       <c r="BM54" s="10" t="n"/>
       <c r="BN54" s="10" t="n"/>
@@ -13556,134 +13822,74 @@
       <c r="BP54" s="10" t="n"/>
       <c r="BQ54" s="11" t="n"/>
     </row>
-    <row r="55" ht="160" customHeight="1">
-      <c r="A55" s="44" t="n">
-        <v>39</v>
-      </c>
-      <c r="B55" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-029-039</t>
-        </is>
-      </c>
+    <row r="55" ht="22.5" customHeight="1">
+      <c r="A55" s="32" t="inlineStr">
+        <is>
+          <t>カテゴリ5: 共通エラーハンドリング（Common Error Handling）</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="n"/>
       <c r="C55" s="10" t="n"/>
-      <c r="D55" s="11" t="n"/>
-      <c r="E55" s="46" t="inlineStr">
-        <is>
-          <t>バリデーションエラー応答形状（VALIDATION_ERROR）</t>
-        </is>
-      </c>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
       <c r="F55" s="10" t="n"/>
       <c r="G55" s="10" t="n"/>
       <c r="H55" s="10" t="n"/>
-      <c r="I55" s="11" t="n"/>
-      <c r="J55" s="46" t="inlineStr">
-        <is>
-          <t>・CHUOKAI でログイン済み</t>
-        </is>
-      </c>
+      <c r="I55" s="10" t="n"/>
+      <c r="J55" s="10" t="n"/>
       <c r="K55" s="10" t="n"/>
       <c r="L55" s="10" t="n"/>
       <c r="M55" s="10" t="n"/>
       <c r="N55" s="10" t="n"/>
       <c r="O55" s="10" t="n"/>
-      <c r="P55" s="11" t="n"/>
-      <c r="Q55" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>DevToolsのNetworkタブでPOST「/api/v1/report/zougen-nichino/export」に tekiyo_date を欠落させたリクエストボディを送信</t>
-          </r>
-        </is>
-      </c>
+      <c r="P55" s="10" t="n"/>
+      <c r="Q55" s="10" t="n"/>
       <c r="R55" s="10" t="n"/>
       <c r="S55" s="10" t="n"/>
       <c r="T55" s="10" t="n"/>
       <c r="U55" s="10" t="n"/>
       <c r="V55" s="10" t="n"/>
-      <c r="W55" s="11" t="n"/>
-      <c r="X55" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・HTTPステータスコード400が返却されること（`error_code: VALIDATION_ERROR`、メッセージ `入力値が不正です。詳細はerrorsフィールドを確認してください。`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・レスポンスに `errors` 配列が含まれ、各要素が `{ field, message }` の形状であること</t>
-          </r>
-        </is>
-      </c>
+      <c r="W55" s="10" t="n"/>
+      <c r="X55" s="10" t="n"/>
       <c r="Y55" s="10" t="n"/>
       <c r="Z55" s="10" t="n"/>
       <c r="AA55" s="10" t="n"/>
       <c r="AB55" s="10" t="n"/>
       <c r="AC55" s="10" t="n"/>
-      <c r="AD55" s="11" t="n"/>
-      <c r="AE55" s="45" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AF55" s="11" t="n"/>
-      <c r="AG55" s="45" t="inlineStr"/>
+      <c r="AD55" s="10" t="n"/>
+      <c r="AE55" s="10" t="n"/>
+      <c r="AF55" s="10" t="n"/>
+      <c r="AG55" s="10" t="n"/>
       <c r="AH55" s="10" t="n"/>
-      <c r="AI55" s="11" t="n"/>
-      <c r="AJ55" s="45" t="inlineStr"/>
+      <c r="AI55" s="10" t="n"/>
+      <c r="AJ55" s="10" t="n"/>
       <c r="AK55" s="10" t="n"/>
-      <c r="AL55" s="11" t="n"/>
-      <c r="AM55" s="45" t="inlineStr"/>
+      <c r="AL55" s="10" t="n"/>
+      <c r="AM55" s="10" t="n"/>
       <c r="AN55" s="10" t="n"/>
-      <c r="AO55" s="11" t="n"/>
-      <c r="AP55" s="45" t="inlineStr"/>
+      <c r="AO55" s="10" t="n"/>
+      <c r="AP55" s="10" t="n"/>
       <c r="AQ55" s="10" t="n"/>
-      <c r="AR55" s="11" t="n"/>
-      <c r="AS55" s="45" t="inlineStr"/>
+      <c r="AR55" s="10" t="n"/>
+      <c r="AS55" s="10" t="n"/>
       <c r="AT55" s="10" t="n"/>
-      <c r="AU55" s="11" t="n"/>
-      <c r="AV55" s="45" t="inlineStr"/>
+      <c r="AU55" s="10" t="n"/>
+      <c r="AV55" s="10" t="n"/>
       <c r="AW55" s="10" t="n"/>
-      <c r="AX55" s="11" t="n"/>
-      <c r="AY55" s="45" t="inlineStr"/>
+      <c r="AX55" s="10" t="n"/>
+      <c r="AY55" s="10" t="n"/>
       <c r="AZ55" s="10" t="n"/>
-      <c r="BA55" s="11" t="n"/>
-      <c r="BB55" s="45" t="inlineStr"/>
+      <c r="BA55" s="10" t="n"/>
+      <c r="BB55" s="10" t="n"/>
       <c r="BC55" s="10" t="n"/>
-      <c r="BD55" s="11" t="n"/>
-      <c r="BE55" s="45" t="inlineStr"/>
+      <c r="BD55" s="10" t="n"/>
+      <c r="BE55" s="10" t="n"/>
       <c r="BF55" s="10" t="n"/>
-      <c r="BG55" s="11" t="n"/>
-      <c r="BH55" s="45" t="inlineStr"/>
+      <c r="BG55" s="10" t="n"/>
+      <c r="BH55" s="10" t="n"/>
       <c r="BI55" s="10" t="n"/>
-      <c r="BJ55" s="11" t="n"/>
-      <c r="BK55" s="46" t="inlineStr"/>
+      <c r="BJ55" s="10" t="n"/>
+      <c r="BK55" s="10" t="n"/>
       <c r="BL55" s="10" t="n"/>
       <c r="BM55" s="10" t="n"/>
       <c r="BN55" s="10" t="n"/>
@@ -13691,20 +13897,20 @@
       <c r="BP55" s="10" t="n"/>
       <c r="BQ55" s="11" t="n"/>
     </row>
-    <row r="56" ht="176" customHeight="1">
+    <row r="56" ht="112" customHeight="1">
       <c r="A56" s="44" t="n">
         <v>40</v>
       </c>
       <c r="B56" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-040</t>
+          <t>ACSMS-TC-029-037</t>
         </is>
       </c>
       <c r="C56" s="10" t="n"/>
       <c r="D56" s="11" t="n"/>
       <c r="E56" s="46" t="inlineStr">
         <is>
-          <t>レート制限超過（TOO_MANY_REQUESTS）</t>
+          <t>不正リクエストパラメータ（BAD_REQUEST）</t>
         </is>
       </c>
       <c r="F56" s="10" t="n"/>
@@ -13738,24 +13944,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">プレビューまたは電子帳票作成相当のリクエストを上限回数まで連続送信する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>上限を超えて追加のリクエストを送信する</t>
+            <t>DevToolsのNetworkタブでGET「/api/v1/report/zougen-nichino/preview?tekiyo_date=2026-03-01&amp;kanri_shiten_id=abc」（数値項目に文字列）を送信</t>
           </r>
         </is>
       </c>
@@ -13781,24 +13970,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">上限回数までのリクエストが正常に処理されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>HTTPステータスコード429が返却されること（`error_code: TOO_MANY_REQUESTS`、メッセージ `リクエスト回数が上限を超えました。しばらくしてから再度お試しください。`）</t>
+            <t>HTTPステータスコード400が返却されること（`error_code: BAD_REQUEST`、メッセージ `リクエストパラメータが不正です。` または `error_code: VALIDATION_ERROR`）</t>
           </r>
         </is>
       </c>
@@ -13852,20 +14024,20 @@
       <c r="BP56" s="10" t="n"/>
       <c r="BQ56" s="11" t="n"/>
     </row>
-    <row r="57" ht="192" customHeight="1">
+    <row r="57" ht="208" customHeight="1">
       <c r="A57" s="44" t="n">
         <v>41</v>
       </c>
       <c r="B57" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-041</t>
+          <t>ACSMS-TC-029-038</t>
         </is>
       </c>
       <c r="C57" s="10" t="n"/>
       <c r="D57" s="11" t="n"/>
       <c r="E57" s="46" t="inlineStr">
         <is>
-          <t>システムエラー（INTERNAL_SERVER_ERROR）</t>
+          <t>セッション切れ（UNAUTHORIZED）</t>
         </is>
       </c>
       <c r="F57" s="10" t="n"/>
@@ -13875,7 +14047,7 @@
       <c r="J57" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・サーバー側で例外を発生させる準備ができている</t>
+・管理ツールでセッションを強制失効させる準備ができている</t>
         </is>
       </c>
       <c r="K57" s="10" t="n"/>
@@ -13900,7 +14072,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>サーバー側でDB接続エラー等を発生させた状態で「レポートプレビュー」を実行する</t>
+            <t xml:space="preserve">増減通知（日本農業新聞）出力画面を開いた状態でセッションを強制失効させる
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>「レポートプレビュー」ボタンをクリックする</t>
           </r>
         </is>
       </c>
@@ -13926,15 +14115,32 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・HTTPステータスコード500が返却されること（`error_code: INTERNAL_SERVER_ERROR`、メッセージ `システムエラーが発生しました。しばらくしてから再度お試しください。`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・メッセージ「システムエラーが発生しました。しばらくしてから再度お試しください。」が表示されること（ACSMS-MSG-029-003）</t>
+            <t xml:space="preserve">画面が表示された状態であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・HTTPステータスコード401が返却されること（`error_code: UNAUTHORIZED`、メッセージ `セッションが切れました。再度ログインしてください。`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・「/login」へ遷移すること（クエリに `redirect` が付与されること）</t>
           </r>
         </is>
       </c>
@@ -13988,20 +14194,20 @@
       <c r="BP57" s="10" t="n"/>
       <c r="BQ57" s="11" t="n"/>
     </row>
-    <row r="58" ht="128" customHeight="1">
+    <row r="58" ht="160" customHeight="1">
       <c r="A58" s="44" t="n">
         <v>42</v>
       </c>
       <c r="B58" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-042</t>
+          <t>ACSMS-TC-029-039</t>
         </is>
       </c>
       <c r="C58" s="10" t="n"/>
       <c r="D58" s="11" t="n"/>
       <c r="E58" s="46" t="inlineStr">
         <is>
-          <t>ネットワーク切断</t>
+          <t>バリデーションエラー応答形状（VALIDATION_ERROR）</t>
         </is>
       </c>
       <c r="F58" s="10" t="n"/>
@@ -14035,24 +14241,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DevToolsのNetworkタブで「Offline」を選択し、ネットワークを切断する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>「レポートプレビュー」ボタンをクリックする</t>
+            <t>DevToolsのNetworkタブでPOST「/api/v1/report/zougen-nichino/export」に tekiyo_date を欠落させたリクエストボディを送信</t>
           </r>
         </is>
       </c>
@@ -14078,32 +14267,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">ネットワークが切断されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・ネットワークエラーのトーストが表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・異常終了しないこと</t>
+            <t xml:space="preserve">・HTTPステータスコード400が返却されること（`error_code: VALIDATION_ERROR`、メッセージ `入力値が不正です。詳細はerrorsフィールドを確認してください。`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・レスポンスに `errors` 配列が含まれ、各要素が `{ field, message }` の形状であること</t>
           </r>
         </is>
       </c>
@@ -14157,20 +14329,20 @@
       <c r="BP58" s="10" t="n"/>
       <c r="BQ58" s="11" t="n"/>
     </row>
-    <row r="59" ht="192" customHeight="1">
+    <row r="59" ht="176" customHeight="1">
       <c r="A59" s="44" t="n">
         <v>43</v>
       </c>
       <c r="B59" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-029-043</t>
+          <t>ACSMS-TC-029-040</t>
         </is>
       </c>
       <c r="C59" s="10" t="n"/>
       <c r="D59" s="11" t="n"/>
       <c r="E59" s="46" t="inlineStr">
         <is>
-          <t>SQLインジェクション入力の安全性</t>
+          <t>レート制限超過（TOO_MANY_REQUESTS）</t>
         </is>
       </c>
       <c r="F59" s="10" t="n"/>
@@ -14204,7 +14376,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DevToolsのNetworkタブでGET「/api/v1/report/zougen-nichino/preview」の tekiyo_date に `2026-03-01'; DROP TABLE t_dokusya_rireki; --` を指定して送信する
+            <t xml:space="preserve">プレビューまたは電子帳票作成相当のリクエストを上限回数まで連続送信する
 </t>
           </r>
           <r>
@@ -14221,7 +14393,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DBで t_dokusya_rireki テーブルが存在することを確認する</t>
+            <t>上限を超えて追加のリクエストを送信する</t>
           </r>
         </is>
       </c>
@@ -14247,15 +14419,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・入力値がパラメータ化クエリにより literal として扱われ、SQLとして実行されないこと
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・HTTPステータスコード400が返却されること（`error_code: VALIDATION_ERROR` または `BAD_REQUEST`）
+            <t xml:space="preserve">上限回数までのリクエストが正常に処理されること
 </t>
           </r>
           <r>
@@ -14272,7 +14436,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>t_dokusya_rireki テーブルが削除されず存在すること</t>
+            <t>HTTPステータスコード429が返却されること（`error_code: TOO_MANY_REQUESTS`、メッセージ `リクエスト回数が上限を超えました。しばらくしてから再度お試しください。`）</t>
           </r>
         </is>
       </c>
@@ -14326,10 +14490,1132 @@
       <c r="BP59" s="10" t="n"/>
       <c r="BQ59" s="11" t="n"/>
     </row>
+    <row r="60" ht="192" customHeight="1">
+      <c r="A60" s="44" t="n">
+        <v>44</v>
+      </c>
+      <c r="B60" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-029-041</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="46" t="inlineStr">
+        <is>
+          <t>システムエラー（INTERNAL_SERVER_ERROR）</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="11" t="n"/>
+      <c r="J60" s="46" t="inlineStr">
+        <is>
+          <t>・CHUOKAI でログイン済み
+・サーバー側で例外を発生させる準備ができている</t>
+        </is>
+      </c>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="11" t="n"/>
+      <c r="Q60" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>サーバー側でDB接続エラー等を発生させた状態で「レポートプレビュー」を実行する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="10" t="n"/>
+      <c r="T60" s="10" t="n"/>
+      <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
+      <c r="W60" s="11" t="n"/>
+      <c r="X60" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・HTTPステータスコード500が返却されること（`error_code: INTERNAL_SERVER_ERROR`、メッセージ `システムエラーが発生しました。しばらくしてから再度お試しください。`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・メッセージ「システムエラーが発生しました。しばらくしてから再度お試しください。」が表示されること（ACSMS-MSG-029-003）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y60" s="10" t="n"/>
+      <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="10" t="n"/>
+      <c r="AB60" s="10" t="n"/>
+      <c r="AC60" s="10" t="n"/>
+      <c r="AD60" s="11" t="n"/>
+      <c r="AE60" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF60" s="11" t="n"/>
+      <c r="AG60" s="45" t="inlineStr"/>
+      <c r="AH60" s="10" t="n"/>
+      <c r="AI60" s="11" t="n"/>
+      <c r="AJ60" s="45" t="inlineStr"/>
+      <c r="AK60" s="10" t="n"/>
+      <c r="AL60" s="11" t="n"/>
+      <c r="AM60" s="45" t="inlineStr"/>
+      <c r="AN60" s="10" t="n"/>
+      <c r="AO60" s="11" t="n"/>
+      <c r="AP60" s="45" t="inlineStr"/>
+      <c r="AQ60" s="10" t="n"/>
+      <c r="AR60" s="11" t="n"/>
+      <c r="AS60" s="45" t="inlineStr"/>
+      <c r="AT60" s="10" t="n"/>
+      <c r="AU60" s="11" t="n"/>
+      <c r="AV60" s="45" t="inlineStr"/>
+      <c r="AW60" s="10" t="n"/>
+      <c r="AX60" s="11" t="n"/>
+      <c r="AY60" s="45" t="inlineStr"/>
+      <c r="AZ60" s="10" t="n"/>
+      <c r="BA60" s="11" t="n"/>
+      <c r="BB60" s="45" t="inlineStr"/>
+      <c r="BC60" s="10" t="n"/>
+      <c r="BD60" s="11" t="n"/>
+      <c r="BE60" s="45" t="inlineStr"/>
+      <c r="BF60" s="10" t="n"/>
+      <c r="BG60" s="11" t="n"/>
+      <c r="BH60" s="45" t="inlineStr"/>
+      <c r="BI60" s="10" t="n"/>
+      <c r="BJ60" s="11" t="n"/>
+      <c r="BK60" s="46" t="inlineStr"/>
+      <c r="BL60" s="10" t="n"/>
+      <c r="BM60" s="10" t="n"/>
+      <c r="BN60" s="10" t="n"/>
+      <c r="BO60" s="10" t="n"/>
+      <c r="BP60" s="10" t="n"/>
+      <c r="BQ60" s="11" t="n"/>
+    </row>
+    <row r="61" ht="128" customHeight="1">
+      <c r="A61" s="44" t="n">
+        <v>45</v>
+      </c>
+      <c r="B61" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-029-042</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="11" t="n"/>
+      <c r="E61" s="46" t="inlineStr">
+        <is>
+          <t>ネットワーク切断</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="11" t="n"/>
+      <c r="J61" s="46" t="inlineStr">
+        <is>
+          <t>・CHUOKAI でログイン済み</t>
+        </is>
+      </c>
+      <c r="K61" s="10" t="n"/>
+      <c r="L61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
+      <c r="P61" s="11" t="n"/>
+      <c r="Q61" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DevToolsのNetworkタブで「Offline」を選択し、ネットワークを切断する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>「レポートプレビュー」ボタンをクリックする</t>
+          </r>
+        </is>
+      </c>
+      <c r="R61" s="10" t="n"/>
+      <c r="S61" s="10" t="n"/>
+      <c r="T61" s="10" t="n"/>
+      <c r="U61" s="10" t="n"/>
+      <c r="V61" s="10" t="n"/>
+      <c r="W61" s="11" t="n"/>
+      <c r="X61" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ネットワークが切断されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・ネットワークエラーのトーストが表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・異常終了しないこと</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y61" s="10" t="n"/>
+      <c r="Z61" s="10" t="n"/>
+      <c r="AA61" s="10" t="n"/>
+      <c r="AB61" s="10" t="n"/>
+      <c r="AC61" s="10" t="n"/>
+      <c r="AD61" s="11" t="n"/>
+      <c r="AE61" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF61" s="11" t="n"/>
+      <c r="AG61" s="45" t="inlineStr"/>
+      <c r="AH61" s="10" t="n"/>
+      <c r="AI61" s="11" t="n"/>
+      <c r="AJ61" s="45" t="inlineStr"/>
+      <c r="AK61" s="10" t="n"/>
+      <c r="AL61" s="11" t="n"/>
+      <c r="AM61" s="45" t="inlineStr"/>
+      <c r="AN61" s="10" t="n"/>
+      <c r="AO61" s="11" t="n"/>
+      <c r="AP61" s="45" t="inlineStr"/>
+      <c r="AQ61" s="10" t="n"/>
+      <c r="AR61" s="11" t="n"/>
+      <c r="AS61" s="45" t="inlineStr"/>
+      <c r="AT61" s="10" t="n"/>
+      <c r="AU61" s="11" t="n"/>
+      <c r="AV61" s="45" t="inlineStr"/>
+      <c r="AW61" s="10" t="n"/>
+      <c r="AX61" s="11" t="n"/>
+      <c r="AY61" s="45" t="inlineStr"/>
+      <c r="AZ61" s="10" t="n"/>
+      <c r="BA61" s="11" t="n"/>
+      <c r="BB61" s="45" t="inlineStr"/>
+      <c r="BC61" s="10" t="n"/>
+      <c r="BD61" s="11" t="n"/>
+      <c r="BE61" s="45" t="inlineStr"/>
+      <c r="BF61" s="10" t="n"/>
+      <c r="BG61" s="11" t="n"/>
+      <c r="BH61" s="45" t="inlineStr"/>
+      <c r="BI61" s="10" t="n"/>
+      <c r="BJ61" s="11" t="n"/>
+      <c r="BK61" s="46" t="inlineStr"/>
+      <c r="BL61" s="10" t="n"/>
+      <c r="BM61" s="10" t="n"/>
+      <c r="BN61" s="10" t="n"/>
+      <c r="BO61" s="10" t="n"/>
+      <c r="BP61" s="10" t="n"/>
+      <c r="BQ61" s="11" t="n"/>
+    </row>
+    <row r="62" ht="192" customHeight="1">
+      <c r="A62" s="44" t="n">
+        <v>46</v>
+      </c>
+      <c r="B62" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-029-043</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="11" t="n"/>
+      <c r="E62" s="46" t="inlineStr">
+        <is>
+          <t>SQLインジェクション入力の安全性</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="10" t="n"/>
+      <c r="I62" s="11" t="n"/>
+      <c r="J62" s="46" t="inlineStr">
+        <is>
+          <t>・CHUOKAI でログイン済み</t>
+        </is>
+      </c>
+      <c r="K62" s="10" t="n"/>
+      <c r="L62" s="10" t="n"/>
+      <c r="M62" s="10" t="n"/>
+      <c r="N62" s="10" t="n"/>
+      <c r="O62" s="10" t="n"/>
+      <c r="P62" s="11" t="n"/>
+      <c r="Q62" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DevToolsのNetworkタブでGET「/api/v1/report/zougen-nichino/preview」の tekiyo_date に `2026-03-01'; DROP TABLE t_dokusya_rireki; --` を指定して送信する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DBで t_dokusya_rireki テーブルが存在することを確認する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R62" s="10" t="n"/>
+      <c r="S62" s="10" t="n"/>
+      <c r="T62" s="10" t="n"/>
+      <c r="U62" s="10" t="n"/>
+      <c r="V62" s="10" t="n"/>
+      <c r="W62" s="11" t="n"/>
+      <c r="X62" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・入力値がパラメータ化クエリにより literal として扱われ、SQLとして実行されないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・HTTPステータスコード400が返却されること（`error_code: VALIDATION_ERROR` または `BAD_REQUEST`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>t_dokusya_rireki テーブルが削除されず存在すること</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y62" s="10" t="n"/>
+      <c r="Z62" s="10" t="n"/>
+      <c r="AA62" s="10" t="n"/>
+      <c r="AB62" s="10" t="n"/>
+      <c r="AC62" s="10" t="n"/>
+      <c r="AD62" s="11" t="n"/>
+      <c r="AE62" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF62" s="11" t="n"/>
+      <c r="AG62" s="45" t="inlineStr"/>
+      <c r="AH62" s="10" t="n"/>
+      <c r="AI62" s="11" t="n"/>
+      <c r="AJ62" s="45" t="inlineStr"/>
+      <c r="AK62" s="10" t="n"/>
+      <c r="AL62" s="11" t="n"/>
+      <c r="AM62" s="45" t="inlineStr"/>
+      <c r="AN62" s="10" t="n"/>
+      <c r="AO62" s="11" t="n"/>
+      <c r="AP62" s="45" t="inlineStr"/>
+      <c r="AQ62" s="10" t="n"/>
+      <c r="AR62" s="11" t="n"/>
+      <c r="AS62" s="45" t="inlineStr"/>
+      <c r="AT62" s="10" t="n"/>
+      <c r="AU62" s="11" t="n"/>
+      <c r="AV62" s="45" t="inlineStr"/>
+      <c r="AW62" s="10" t="n"/>
+      <c r="AX62" s="11" t="n"/>
+      <c r="AY62" s="45" t="inlineStr"/>
+      <c r="AZ62" s="10" t="n"/>
+      <c r="BA62" s="11" t="n"/>
+      <c r="BB62" s="45" t="inlineStr"/>
+      <c r="BC62" s="10" t="n"/>
+      <c r="BD62" s="11" t="n"/>
+      <c r="BE62" s="45" t="inlineStr"/>
+      <c r="BF62" s="10" t="n"/>
+      <c r="BG62" s="11" t="n"/>
+      <c r="BH62" s="45" t="inlineStr"/>
+      <c r="BI62" s="10" t="n"/>
+      <c r="BJ62" s="11" t="n"/>
+      <c r="BK62" s="46" t="inlineStr"/>
+      <c r="BL62" s="10" t="n"/>
+      <c r="BM62" s="10" t="n"/>
+      <c r="BN62" s="10" t="n"/>
+      <c r="BO62" s="10" t="n"/>
+      <c r="BP62" s="10" t="n"/>
+      <c r="BQ62" s="11" t="n"/>
+    </row>
+    <row r="63" ht="450" customHeight="1">
+      <c r="A63" s="44" t="n">
+        <v>47</v>
+      </c>
+      <c r="B63" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-029-047</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="46" t="inlineStr">
+        <is>
+          <t>ページ送り（15販売店行/ページ・別API・PDFと一致）</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="11" t="n"/>
+      <c r="J63" s="46" t="inlineStr">
+        <is>
+          <t>・CHUOKAI でログイン済み
+・当該適用日に 16 名以上の増減対象購読者が存在する</t>
+        </is>
+      </c>
+      <c r="K63" s="10" t="n"/>
+      <c r="L63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="10" t="n"/>
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="11" t="n"/>
+      <c r="Q63" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">適用日を入力して「レポートプレビュー」を実行する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">プレビュー下部のページャで 2 ページ目に移動する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>同条件で「電子帳票作成」を実行し、出力PDFのページ構成を確認する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R63" s="10" t="n"/>
+      <c r="S63" s="10" t="n"/>
+      <c r="T63" s="10" t="n"/>
+      <c r="U63" s="10" t="n"/>
+      <c r="V63" s="10" t="n"/>
+      <c r="W63" s="11" t="n"/>
+      <c r="X63" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・1ページ目に **15 販売店行**まで表示されること（≒15購読者。大半1行/購読者。販売店変更=2行になり得るため厳密に15行ではない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・ページャ（全N件＝対象購読者数・1/M ページ）が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・帳票ヘッダの「Page」が `1/M` であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・BEは `COUNT(DISTINCT dokusya_id)` ＋ `dokusya_id` の OFFSET/LIMIT で1ページ分の購読者の明細だけをロードすること（全件ロードではない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・2 ページ目を別APIで再取得し、残りの購読者が表示されること（ブラウザは1ページ分のみ描画）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・「Page」が `2/M` に更新されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・出力PDFの n ページ目が、プレビューの n ページ目と同じ内容・同じ改ページであること（全管理支店を1つのPDFにまとめ、ページ先頭でのみ改ページ）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y63" s="10" t="n"/>
+      <c r="Z63" s="10" t="n"/>
+      <c r="AA63" s="10" t="n"/>
+      <c r="AB63" s="10" t="n"/>
+      <c r="AC63" s="10" t="n"/>
+      <c r="AD63" s="11" t="n"/>
+      <c r="AE63" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF63" s="11" t="n"/>
+      <c r="AG63" s="45" t="inlineStr"/>
+      <c r="AH63" s="10" t="n"/>
+      <c r="AI63" s="11" t="n"/>
+      <c r="AJ63" s="45" t="inlineStr"/>
+      <c r="AK63" s="10" t="n"/>
+      <c r="AL63" s="11" t="n"/>
+      <c r="AM63" s="45" t="inlineStr"/>
+      <c r="AN63" s="10" t="n"/>
+      <c r="AO63" s="11" t="n"/>
+      <c r="AP63" s="45" t="inlineStr"/>
+      <c r="AQ63" s="10" t="n"/>
+      <c r="AR63" s="11" t="n"/>
+      <c r="AS63" s="45" t="inlineStr"/>
+      <c r="AT63" s="10" t="n"/>
+      <c r="AU63" s="11" t="n"/>
+      <c r="AV63" s="45" t="inlineStr"/>
+      <c r="AW63" s="10" t="n"/>
+      <c r="AX63" s="11" t="n"/>
+      <c r="AY63" s="45" t="inlineStr"/>
+      <c r="AZ63" s="10" t="n"/>
+      <c r="BA63" s="11" t="n"/>
+      <c r="BB63" s="45" t="inlineStr"/>
+      <c r="BC63" s="10" t="n"/>
+      <c r="BD63" s="11" t="n"/>
+      <c r="BE63" s="45" t="inlineStr"/>
+      <c r="BF63" s="10" t="n"/>
+      <c r="BG63" s="11" t="n"/>
+      <c r="BH63" s="45" t="inlineStr"/>
+      <c r="BI63" s="10" t="n"/>
+      <c r="BJ63" s="11" t="n"/>
+      <c r="BK63" s="46" t="inlineStr">
+        <is>
+          <t>各管理支店の合計はそのページの行から算出する（管理支店がページをまたぐ場合はページ内合計）。</t>
+        </is>
+      </c>
+      <c r="BL63" s="10" t="n"/>
+      <c r="BM63" s="10" t="n"/>
+      <c r="BN63" s="10" t="n"/>
+      <c r="BO63" s="10" t="n"/>
+      <c r="BP63" s="10" t="n"/>
+      <c r="BQ63" s="11" t="n"/>
+    </row>
+    <row r="64" ht="22.5" customHeight="1">
+      <c r="A64" s="32" t="inlineStr">
+        <is>
+          <t>カテゴリ6: 集計対象（Scope）</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="10" t="n"/>
+      <c r="J64" s="10" t="n"/>
+      <c r="K64" s="10" t="n"/>
+      <c r="L64" s="10" t="n"/>
+      <c r="M64" s="10" t="n"/>
+      <c r="N64" s="10" t="n"/>
+      <c r="O64" s="10" t="n"/>
+      <c r="P64" s="10" t="n"/>
+      <c r="Q64" s="10" t="n"/>
+      <c r="R64" s="10" t="n"/>
+      <c r="S64" s="10" t="n"/>
+      <c r="T64" s="10" t="n"/>
+      <c r="U64" s="10" t="n"/>
+      <c r="V64" s="10" t="n"/>
+      <c r="W64" s="10" t="n"/>
+      <c r="X64" s="10" t="n"/>
+      <c r="Y64" s="10" t="n"/>
+      <c r="Z64" s="10" t="n"/>
+      <c r="AA64" s="10" t="n"/>
+      <c r="AB64" s="10" t="n"/>
+      <c r="AC64" s="10" t="n"/>
+      <c r="AD64" s="10" t="n"/>
+      <c r="AE64" s="10" t="n"/>
+      <c r="AF64" s="10" t="n"/>
+      <c r="AG64" s="10" t="n"/>
+      <c r="AH64" s="10" t="n"/>
+      <c r="AI64" s="10" t="n"/>
+      <c r="AJ64" s="10" t="n"/>
+      <c r="AK64" s="10" t="n"/>
+      <c r="AL64" s="10" t="n"/>
+      <c r="AM64" s="10" t="n"/>
+      <c r="AN64" s="10" t="n"/>
+      <c r="AO64" s="10" t="n"/>
+      <c r="AP64" s="10" t="n"/>
+      <c r="AQ64" s="10" t="n"/>
+      <c r="AR64" s="10" t="n"/>
+      <c r="AS64" s="10" t="n"/>
+      <c r="AT64" s="10" t="n"/>
+      <c r="AU64" s="10" t="n"/>
+      <c r="AV64" s="10" t="n"/>
+      <c r="AW64" s="10" t="n"/>
+      <c r="AX64" s="10" t="n"/>
+      <c r="AY64" s="10" t="n"/>
+      <c r="AZ64" s="10" t="n"/>
+      <c r="BA64" s="10" t="n"/>
+      <c r="BB64" s="10" t="n"/>
+      <c r="BC64" s="10" t="n"/>
+      <c r="BD64" s="10" t="n"/>
+      <c r="BE64" s="10" t="n"/>
+      <c r="BF64" s="10" t="n"/>
+      <c r="BG64" s="10" t="n"/>
+      <c r="BH64" s="10" t="n"/>
+      <c r="BI64" s="10" t="n"/>
+      <c r="BJ64" s="10" t="n"/>
+      <c r="BK64" s="10" t="n"/>
+      <c r="BL64" s="10" t="n"/>
+      <c r="BM64" s="10" t="n"/>
+      <c r="BN64" s="10" t="n"/>
+      <c r="BO64" s="10" t="n"/>
+      <c r="BP64" s="10" t="n"/>
+      <c r="BQ64" s="11" t="n"/>
+    </row>
+    <row r="65" ht="450" customHeight="1">
+      <c r="A65" s="44" t="n">
+        <v>48</v>
+      </c>
+      <c r="B65" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-029-048</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="46" t="inlineStr">
+        <is>
+          <t>集計対象を紙版のみに限定（#56410）</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="11" t="n"/>
+      <c r="J65" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN（`report.export_zougen_nichino` 権限あり）
+・適用日を 2026/09/01 とし、同日に増減報告対象（`zougen_hokoku_flg = true`）の履歴を持つ購読者を以下のとおり用意すること（いずれも実在の販売店 A・同一管理支店の配下）
+・(a) 紙版（dokusya_shubetsu=1）で 1 → 3 部の増部 1件
+・(b) 併読（3）で部数変更 1件
+・(c) 電子版（2）・承認済（denshi_shonin_status=1）1件
+・(d) 電子版（2）・未承認 1件</t>
+        </is>
+      </c>
+      <c r="K65" s="10" t="n"/>
+      <c r="L65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
+      <c r="N65" s="10" t="n"/>
+      <c r="O65" s="10" t="n"/>
+      <c r="P65" s="11" t="n"/>
+      <c r="Q65" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">適用日 2026/09/01 でプレビューを表示し、集計に載る販売店行と部数を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">PDF を出力し、販売店 A の増部数・減部数・差引を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(b) 併読の変動が部数に反映されているか確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(c) 電子版・承認済の変動が部数に反映されているか確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(a) のみを残し他を削除した状態で出力し、部数が変わらないことを確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>同じ条件で SCR-028 増減連絡票（販売店）を出力し、対象購読者が一致することを確認する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R65" s="10" t="n"/>
+      <c r="S65" s="10" t="n"/>
+      <c r="T65" s="10" t="n"/>
+      <c r="U65" s="10" t="n"/>
+      <c r="V65" s="10" t="n"/>
+      <c r="W65" s="11" t="n"/>
+      <c r="X65" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">販売店 A の増部数が **(a) の増分（+2部）のみ**で構成されていること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">PDF の値がプレビューと一致すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">**反映されないこと**。本帳票も部数の増減を伝えるものであり、併読は配達を伴わないため対象外
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">**反映されないこと**。従来の「電子版は承認済のみ集計」条件は紙版限定に包含されるため廃止された（顧客要件2026-08 / #56410）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">出力内容が変わらないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">両帳票で対象となる購読者が一致すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・SCR-028 増減連絡票（販売店）と同方針だが、**条件は各画面が個別に持つ**（共通化していないため、片方だけ変更されると乖離する）。ステップ6はその乖離を検出するための確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・本画面は出力条件に販売店の入力欄が無いため、ダミー販売店の表示制御（#56597）は対象外。ただし集計SQL側では `h.haiten_flg = false` により廃店・ダミー販売店を除外している
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・購読者名簿（SCR-026）は帳票種別ごとに対象が異なる（管理支店別は併読・電子版も対象）。本画面の条件をそのまま流用しないこと</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y65" s="10" t="n"/>
+      <c r="Z65" s="10" t="n"/>
+      <c r="AA65" s="10" t="n"/>
+      <c r="AB65" s="10" t="n"/>
+      <c r="AC65" s="10" t="n"/>
+      <c r="AD65" s="11" t="n"/>
+      <c r="AE65" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF65" s="11" t="n"/>
+      <c r="AG65" s="45" t="inlineStr"/>
+      <c r="AH65" s="10" t="n"/>
+      <c r="AI65" s="11" t="n"/>
+      <c r="AJ65" s="45" t="inlineStr"/>
+      <c r="AK65" s="10" t="n"/>
+      <c r="AL65" s="11" t="n"/>
+      <c r="AM65" s="45" t="inlineStr"/>
+      <c r="AN65" s="10" t="n"/>
+      <c r="AO65" s="11" t="n"/>
+      <c r="AP65" s="45" t="inlineStr"/>
+      <c r="AQ65" s="10" t="n"/>
+      <c r="AR65" s="11" t="n"/>
+      <c r="AS65" s="45" t="inlineStr"/>
+      <c r="AT65" s="10" t="n"/>
+      <c r="AU65" s="11" t="n"/>
+      <c r="AV65" s="45" t="inlineStr"/>
+      <c r="AW65" s="10" t="n"/>
+      <c r="AX65" s="11" t="n"/>
+      <c r="AY65" s="45" t="inlineStr"/>
+      <c r="AZ65" s="10" t="n"/>
+      <c r="BA65" s="11" t="n"/>
+      <c r="BB65" s="45" t="inlineStr"/>
+      <c r="BC65" s="10" t="n"/>
+      <c r="BD65" s="11" t="n"/>
+      <c r="BE65" s="45" t="inlineStr"/>
+      <c r="BF65" s="10" t="n"/>
+      <c r="BG65" s="11" t="n"/>
+      <c r="BH65" s="45" t="inlineStr"/>
+      <c r="BI65" s="10" t="n"/>
+      <c r="BJ65" s="11" t="n"/>
+      <c r="BK65" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL65" s="10" t="n"/>
+      <c r="BM65" s="10" t="n"/>
+      <c r="BN65" s="10" t="n"/>
+      <c r="BO65" s="10" t="n"/>
+      <c r="BP65" s="10" t="n"/>
+      <c r="BQ65" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="802">
+  <mergeCells count="888">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
+    <mergeCell ref="B60:D60"/>
     <mergeCell ref="Q27:W27"/>
     <mergeCell ref="AS46:AU46"/>
     <mergeCell ref="BK58:BQ58"/>
@@ -14338,12 +15624,16 @@
     <mergeCell ref="BH33:BJ33"/>
     <mergeCell ref="BK50:BQ50"/>
     <mergeCell ref="AE41:AF41"/>
+    <mergeCell ref="E52:I52"/>
+    <mergeCell ref="B53:D53"/>
     <mergeCell ref="AV57:AX57"/>
-    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="AP60:AR60"/>
     <mergeCell ref="E39:I39"/>
     <mergeCell ref="E14:I14"/>
+    <mergeCell ref="AS61:AU61"/>
     <mergeCell ref="W7:Y7"/>
     <mergeCell ref="AS48:AU48"/>
+    <mergeCell ref="J62:P62"/>
     <mergeCell ref="BK16:BQ16"/>
     <mergeCell ref="AE56:AF56"/>
     <mergeCell ref="AE43:AF43"/>
@@ -14353,6 +15643,7 @@
     <mergeCell ref="W8:Y8"/>
     <mergeCell ref="Q37:W37"/>
     <mergeCell ref="AJ20:AL20"/>
+    <mergeCell ref="AM65:AO65"/>
     <mergeCell ref="AG24:AI24"/>
     <mergeCell ref="BH39:BJ39"/>
     <mergeCell ref="J57:P57"/>
@@ -14380,6 +15671,7 @@
     <mergeCell ref="BK48:BQ48"/>
     <mergeCell ref="AM49:AO49"/>
     <mergeCell ref="AE50:AF50"/>
+    <mergeCell ref="AG52:AI52"/>
     <mergeCell ref="BE22:BG22"/>
     <mergeCell ref="BH23:BJ23"/>
     <mergeCell ref="BB26:BD26"/>
@@ -14390,15 +15682,17 @@
     <mergeCell ref="E20:I20"/>
     <mergeCell ref="J39:P39"/>
     <mergeCell ref="AG37:AI37"/>
+    <mergeCell ref="AE62:AF62"/>
     <mergeCell ref="AG47:AI47"/>
     <mergeCell ref="AF8:AH8"/>
     <mergeCell ref="BB27:BD27"/>
     <mergeCell ref="AY31:BA31"/>
     <mergeCell ref="BK37:BQ37"/>
-    <mergeCell ref="AM55:AO55"/>
     <mergeCell ref="BH34:BJ34"/>
     <mergeCell ref="X23:AD23"/>
     <mergeCell ref="BE38:BG38"/>
+    <mergeCell ref="AS62:AU62"/>
+    <mergeCell ref="AV63:AX63"/>
     <mergeCell ref="BH49:BJ49"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AP53:AR53"/>
@@ -14406,9 +15700,12 @@
     <mergeCell ref="AP28:AR28"/>
     <mergeCell ref="AE57:AF57"/>
     <mergeCell ref="BK53:BQ53"/>
+    <mergeCell ref="BH60:BJ60"/>
     <mergeCell ref="AC7:AE7"/>
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
+    <mergeCell ref="J65:P65"/>
+    <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="X18:AD18"/>
     <mergeCell ref="BE33:BG33"/>
     <mergeCell ref="BB37:BD37"/>
@@ -14420,12 +15717,13 @@
     <mergeCell ref="Q59:W59"/>
     <mergeCell ref="J25:P25"/>
     <mergeCell ref="Q46:W46"/>
-    <mergeCell ref="BH55:BJ55"/>
     <mergeCell ref="AM24:AO24"/>
     <mergeCell ref="AG27:AI27"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="AM60:AO60"/>
     <mergeCell ref="BB38:BD38"/>
     <mergeCell ref="AV14:AX14"/>
+    <mergeCell ref="Q61:W61"/>
     <mergeCell ref="W3:AH3"/>
     <mergeCell ref="E33:I33"/>
     <mergeCell ref="Q48:W48"/>
@@ -14440,6 +15738,7 @@
     <mergeCell ref="BH44:BJ44"/>
     <mergeCell ref="AS19:AU19"/>
     <mergeCell ref="Q56:W56"/>
+    <mergeCell ref="AE52:AF52"/>
     <mergeCell ref="Q43:W43"/>
     <mergeCell ref="J14:P14"/>
     <mergeCell ref="AE39:AF39"/>
@@ -14458,16 +15757,14 @@
     <mergeCell ref="J53:P53"/>
     <mergeCell ref="AS14:AU14"/>
     <mergeCell ref="AE53:AF53"/>
-    <mergeCell ref="AG55:AI55"/>
+    <mergeCell ref="AJ56:AL56"/>
     <mergeCell ref="AP18:AR18"/>
-    <mergeCell ref="AJ56:AL56"/>
     <mergeCell ref="BH26:BJ26"/>
     <mergeCell ref="AG38:AI38"/>
     <mergeCell ref="BE30:BG30"/>
     <mergeCell ref="AJ43:AL43"/>
     <mergeCell ref="AV25:AX25"/>
     <mergeCell ref="W6:Y6"/>
-    <mergeCell ref="J55:P55"/>
     <mergeCell ref="BK28:BQ28"/>
     <mergeCell ref="AY32:BA32"/>
     <mergeCell ref="BB33:BD33"/>
@@ -14481,6 +15778,7 @@
     <mergeCell ref="Q36:W36"/>
     <mergeCell ref="BE54:BG54"/>
     <mergeCell ref="Q30:W30"/>
+    <mergeCell ref="AE63:AF63"/>
     <mergeCell ref="X26:AD26"/>
     <mergeCell ref="W1:AH1"/>
     <mergeCell ref="AC8:AE8"/>
@@ -14491,12 +15789,16 @@
     <mergeCell ref="J33:P33"/>
     <mergeCell ref="AE58:AF58"/>
     <mergeCell ref="BB59:BD59"/>
+    <mergeCell ref="AM63:AO63"/>
     <mergeCell ref="X27:AD27"/>
     <mergeCell ref="BB46:BD46"/>
     <mergeCell ref="BE57:BG57"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="AY60:BA60"/>
+    <mergeCell ref="BB61:BD61"/>
     <mergeCell ref="AV15:AX15"/>
     <mergeCell ref="AY16:BA16"/>
+    <mergeCell ref="Q62:W62"/>
     <mergeCell ref="E34:I34"/>
     <mergeCell ref="BB48:BD48"/>
     <mergeCell ref="AG43:AI43"/>
@@ -14509,6 +15811,7 @@
     <mergeCell ref="E36:I36"/>
     <mergeCell ref="Q51:W51"/>
     <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AV65:AX65"/>
     <mergeCell ref="BH45:BJ45"/>
     <mergeCell ref="AS20:AU20"/>
     <mergeCell ref="AP24:AR24"/>
@@ -14522,7 +15825,6 @@
     <mergeCell ref="AP26:AR26"/>
     <mergeCell ref="X14:AD14"/>
     <mergeCell ref="AY42:BA42"/>
-    <mergeCell ref="AE55:AF55"/>
     <mergeCell ref="X38:AD38"/>
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="BH46:BJ46"/>
@@ -14530,6 +15832,7 @@
     <mergeCell ref="BE44:BG44"/>
     <mergeCell ref="AP19:AR19"/>
     <mergeCell ref="AJ57:AL57"/>
+    <mergeCell ref="AG61:AI61"/>
     <mergeCell ref="BE31:BG31"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="AG48:AI48"/>
@@ -14544,6 +15847,7 @@
     <mergeCell ref="BK44:BQ44"/>
     <mergeCell ref="AY48:BA48"/>
     <mergeCell ref="BB49:BD49"/>
+    <mergeCell ref="AG62:AI62"/>
     <mergeCell ref="AE33:AF33"/>
     <mergeCell ref="BB36:BD36"/>
     <mergeCell ref="X40:AD40"/>
@@ -14552,6 +15856,7 @@
     <mergeCell ref="T6:V6"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="AV30:AX30"/>
+    <mergeCell ref="Q52:W52"/>
     <mergeCell ref="Q39:W39"/>
     <mergeCell ref="AS33:AU33"/>
     <mergeCell ref="AM36:AO36"/>
@@ -14560,8 +15865,10 @@
     <mergeCell ref="J34:P34"/>
     <mergeCell ref="E26:I26"/>
     <mergeCell ref="AY37:BA37"/>
+    <mergeCell ref="BE65:BG65"/>
     <mergeCell ref="J49:P49"/>
     <mergeCell ref="J36:P36"/>
+    <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
     <mergeCell ref="AY53:BA53"/>
@@ -14570,11 +15877,12 @@
     <mergeCell ref="E50:I50"/>
     <mergeCell ref="AG11:AI11"/>
     <mergeCell ref="BH53:BJ53"/>
+    <mergeCell ref="Q65:W65"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="AV23:AX23"/>
     <mergeCell ref="BB51:BD51"/>
+    <mergeCell ref="AP63:AR63"/>
     <mergeCell ref="E42:I42"/>
-    <mergeCell ref="AY55:BA55"/>
     <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="E44:I44"/>
@@ -14583,6 +15891,7 @@
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="AV24:AX24"/>
     <mergeCell ref="BE58:BG58"/>
+    <mergeCell ref="AJ65:AL65"/>
     <mergeCell ref="T8:V8"/>
     <mergeCell ref="AP27:AR27"/>
     <mergeCell ref="AS28:AU28"/>
@@ -14598,6 +15907,7 @@
     <mergeCell ref="AJ25:AL25"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="BE53:BG53"/>
+    <mergeCell ref="AJ60:AL60"/>
     <mergeCell ref="AM32:AO32"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="AM26:AO26"/>
@@ -14610,6 +15920,7 @@
     <mergeCell ref="E57:I57"/>
     <mergeCell ref="AV50:AX50"/>
     <mergeCell ref="B46:D46"/>
+    <mergeCell ref="Q60:W60"/>
     <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="E32:I32"/>
     <mergeCell ref="J26:P26"/>
@@ -14617,35 +15928,44 @@
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="AV55:AX55"/>
+    <mergeCell ref="AG65:AI65"/>
     <mergeCell ref="E47:I47"/>
     <mergeCell ref="BB39:BD39"/>
     <mergeCell ref="B48:D48"/>
-    <mergeCell ref="AP55:AR55"/>
+    <mergeCell ref="AV52:AX52"/>
     <mergeCell ref="AS56:AU56"/>
     <mergeCell ref="AP38:AR38"/>
     <mergeCell ref="X41:AD41"/>
     <mergeCell ref="AS43:AU43"/>
+    <mergeCell ref="AY63:BA63"/>
     <mergeCell ref="BE25:BG25"/>
     <mergeCell ref="BK38:BQ38"/>
     <mergeCell ref="F4:AH4"/>
     <mergeCell ref="X51:AD51"/>
     <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="AM52:AO52"/>
+    <mergeCell ref="BH61:BJ61"/>
     <mergeCell ref="AG17:AI17"/>
     <mergeCell ref="AS36:AU36"/>
     <mergeCell ref="J50:P50"/>
     <mergeCell ref="AM39:AO39"/>
     <mergeCell ref="AP40:AR40"/>
     <mergeCell ref="J42:P42"/>
+    <mergeCell ref="BK63:BQ63"/>
     <mergeCell ref="AJ15:AL15"/>
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="AG19:AI19"/>
     <mergeCell ref="X36:AD36"/>
+    <mergeCell ref="J52:P52"/>
     <mergeCell ref="J44:P44"/>
     <mergeCell ref="Q25:W25"/>
     <mergeCell ref="AV37:AX37"/>
+    <mergeCell ref="BB65:BD65"/>
+    <mergeCell ref="E60:I60"/>
     <mergeCell ref="J37:P37"/>
+    <mergeCell ref="AV60:AX60"/>
     <mergeCell ref="Q33:W33"/>
+    <mergeCell ref="X61:AD61"/>
     <mergeCell ref="BK27:BQ27"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="AV45:AX45"/>
@@ -14655,6 +15975,7 @@
     <mergeCell ref="AV26:AX26"/>
     <mergeCell ref="E45:I45"/>
     <mergeCell ref="AM42:AO42"/>
+    <mergeCell ref="X62:AD62"/>
     <mergeCell ref="AE37:AF37"/>
     <mergeCell ref="BH16:BJ16"/>
     <mergeCell ref="BB19:BD19"/>
@@ -14662,14 +15983,15 @@
     <mergeCell ref="AE24:AF24"/>
     <mergeCell ref="AS44:AU44"/>
     <mergeCell ref="AV27:AX27"/>
-    <mergeCell ref="BE55:BG55"/>
     <mergeCell ref="AS31:AU31"/>
     <mergeCell ref="BH18:BJ18"/>
     <mergeCell ref="J32:P32"/>
+    <mergeCell ref="J63:P63"/>
     <mergeCell ref="AE26:AF26"/>
     <mergeCell ref="AY38:BA38"/>
     <mergeCell ref="Q22:W22"/>
     <mergeCell ref="BB58:BD58"/>
+    <mergeCell ref="B61:D61"/>
     <mergeCell ref="J47:P47"/>
     <mergeCell ref="AV58:AX58"/>
     <mergeCell ref="BB20:BD20"/>
@@ -14677,7 +15999,7 @@
     <mergeCell ref="AY24:BA24"/>
     <mergeCell ref="AJ28:AL28"/>
     <mergeCell ref="BK17:BQ17"/>
-    <mergeCell ref="BK55:BQ55"/>
+    <mergeCell ref="BB60:BD60"/>
     <mergeCell ref="AP30:AR30"/>
     <mergeCell ref="AP59:AR59"/>
     <mergeCell ref="AJ30:AL30"/>
@@ -14689,6 +16011,7 @@
     <mergeCell ref="AS57:AU57"/>
     <mergeCell ref="AY19:BA19"/>
     <mergeCell ref="BK25:BQ25"/>
+    <mergeCell ref="AP61:AR61"/>
     <mergeCell ref="AM16:AO16"/>
     <mergeCell ref="AP48:AR48"/>
     <mergeCell ref="AE44:AF44"/>
@@ -14696,6 +16019,7 @@
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="AP41:AR41"/>
     <mergeCell ref="AM18:AO18"/>
+    <mergeCell ref="J60:P60"/>
     <mergeCell ref="BK41:BQ41"/>
     <mergeCell ref="BB13:BD13"/>
     <mergeCell ref="AM17:AO17"/>
@@ -14719,7 +16043,6 @@
     <mergeCell ref="AM44:AO44"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="AF6:AH6"/>
-    <mergeCell ref="E55:I55"/>
     <mergeCell ref="AE32:AF32"/>
     <mergeCell ref="AV48:AX48"/>
     <mergeCell ref="AY14:BA14"/>
@@ -14749,17 +16072,22 @@
     <mergeCell ref="AY54:BA54"/>
     <mergeCell ref="AG33:AI33"/>
     <mergeCell ref="X17:AD17"/>
+    <mergeCell ref="BK61:BQ61"/>
     <mergeCell ref="AJ44:AL44"/>
     <mergeCell ref="Q54:W54"/>
+    <mergeCell ref="AS65:AU65"/>
     <mergeCell ref="BE18:BG18"/>
     <mergeCell ref="AY27:BA27"/>
     <mergeCell ref="AJ31:AL31"/>
+    <mergeCell ref="B62:D62"/>
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
     <mergeCell ref="X19:AD19"/>
+    <mergeCell ref="AE60:AF60"/>
     <mergeCell ref="AS58:AU58"/>
     <mergeCell ref="AG34:AI34"/>
     <mergeCell ref="AV59:AX59"/>
+    <mergeCell ref="AP62:AR62"/>
     <mergeCell ref="E16:I16"/>
     <mergeCell ref="AV46:AX46"/>
     <mergeCell ref="Q31:W31"/>
@@ -14767,16 +16095,21 @@
     <mergeCell ref="AS50:AU50"/>
     <mergeCell ref="E10:I11"/>
     <mergeCell ref="BK56:BQ56"/>
+    <mergeCell ref="BK62:BQ62"/>
     <mergeCell ref="BE36:BG36"/>
     <mergeCell ref="BH37:BJ37"/>
     <mergeCell ref="AE45:AF45"/>
     <mergeCell ref="X58:AD58"/>
+    <mergeCell ref="AS60:AU60"/>
+    <mergeCell ref="AV61:AX61"/>
     <mergeCell ref="Z7:AB7"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AP51:AR51"/>
     <mergeCell ref="AG59:AI59"/>
     <mergeCell ref="BK51:BQ51"/>
+    <mergeCell ref="X60:AD60"/>
+    <mergeCell ref="AM61:AO61"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="BB54:BD54"/>
     <mergeCell ref="AE59:AF59"/>
@@ -14786,9 +16119,11 @@
     <mergeCell ref="AE46:AF46"/>
     <mergeCell ref="BH51:BJ51"/>
     <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AP65:AR65"/>
     <mergeCell ref="AM20:AO20"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="B19:D19"/>
+    <mergeCell ref="J61:P61"/>
     <mergeCell ref="AY11:BA11"/>
     <mergeCell ref="Q57:W57"/>
     <mergeCell ref="J48:P48"/>
@@ -14806,7 +16141,6 @@
     <mergeCell ref="AS15:AU15"/>
     <mergeCell ref="AE48:AF48"/>
     <mergeCell ref="BH27:BJ27"/>
-    <mergeCell ref="AS55:AU55"/>
     <mergeCell ref="BE37:BG37"/>
     <mergeCell ref="AJ50:AL50"/>
     <mergeCell ref="BH20:BJ20"/>
@@ -14819,7 +16153,9 @@
     <mergeCell ref="AG41:AI41"/>
     <mergeCell ref="AP39:AR39"/>
     <mergeCell ref="AP14:AR14"/>
+    <mergeCell ref="AJ52:AL52"/>
     <mergeCell ref="BH22:BJ22"/>
+    <mergeCell ref="BK52:BQ52"/>
     <mergeCell ref="AG56:AI56"/>
     <mergeCell ref="BE26:BG26"/>
     <mergeCell ref="J16:P16"/>
@@ -14848,18 +16184,24 @@
     <mergeCell ref="Q47:W47"/>
     <mergeCell ref="BH13:BJ13"/>
     <mergeCell ref="E19:I19"/>
+    <mergeCell ref="BE52:BG52"/>
+    <mergeCell ref="BK65:BQ65"/>
     <mergeCell ref="BB56:BD56"/>
+    <mergeCell ref="AE61:AF61"/>
     <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="BH15:BJ15"/>
     <mergeCell ref="AY30:BA30"/>
     <mergeCell ref="AJ32:AL32"/>
+    <mergeCell ref="AJ63:AL63"/>
     <mergeCell ref="AP25:AR25"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="AY46:BA46"/>
     <mergeCell ref="BB57:BD57"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="Q58:W58"/>
+    <mergeCell ref="AY61:BA61"/>
     <mergeCell ref="AV16:AX16"/>
+    <mergeCell ref="Q63:W63"/>
     <mergeCell ref="AJ40:AL40"/>
     <mergeCell ref="Q50:W50"/>
     <mergeCell ref="AJ27:AL27"/>
@@ -14877,13 +16219,16 @@
     <mergeCell ref="AP20:AR20"/>
     <mergeCell ref="AY43:BA43"/>
     <mergeCell ref="BE32:BG32"/>
+    <mergeCell ref="BE63:BG63"/>
     <mergeCell ref="BK14:BQ14"/>
     <mergeCell ref="AE16:AF16"/>
     <mergeCell ref="AG32:AI32"/>
+    <mergeCell ref="A64:BQ64"/>
     <mergeCell ref="AE10:AF11"/>
     <mergeCell ref="BH43:BJ43"/>
     <mergeCell ref="BE47:BG47"/>
     <mergeCell ref="AP22:AR22"/>
+    <mergeCell ref="BK60:BQ60"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="J18:P18"/>
     <mergeCell ref="AE18:AF18"/>
@@ -14900,8 +16245,9 @@
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="AJ45:AL45"/>
     <mergeCell ref="AG57:AI57"/>
+    <mergeCell ref="E63:I63"/>
     <mergeCell ref="B15:D15"/>
-    <mergeCell ref="AJ55:AL55"/>
+    <mergeCell ref="BB52:BD52"/>
     <mergeCell ref="AY34:BA34"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="J19:P19"/>
@@ -14911,7 +16257,6 @@
     <mergeCell ref="BB45:BD45"/>
     <mergeCell ref="AG58:AI58"/>
     <mergeCell ref="BB32:BD32"/>
-    <mergeCell ref="Q55:W55"/>
     <mergeCell ref="AY36:BA36"/>
     <mergeCell ref="E27:I27"/>
     <mergeCell ref="AS49:AU49"/>
@@ -14919,6 +16264,7 @@
     <mergeCell ref="X28:AD28"/>
     <mergeCell ref="AS30:AU30"/>
     <mergeCell ref="BB47:BD47"/>
+    <mergeCell ref="AG60:AI60"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="AS42:AU42"/>
     <mergeCell ref="A35:BQ35"/>
@@ -14928,6 +16274,7 @@
     <mergeCell ref="X30:AD30"/>
     <mergeCell ref="BE45:BG45"/>
     <mergeCell ref="AJ58:AL58"/>
+    <mergeCell ref="BH65:BJ65"/>
     <mergeCell ref="X42:AD42"/>
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="BH56:BJ56"/>
@@ -14935,6 +16282,8 @@
     <mergeCell ref="AJ48:AL48"/>
     <mergeCell ref="AV42:AX42"/>
     <mergeCell ref="BE59:BG59"/>
+    <mergeCell ref="AY62:BA62"/>
+    <mergeCell ref="BB63:BD63"/>
     <mergeCell ref="BE46:BG46"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
@@ -14969,28 +16318,31 @@
     <mergeCell ref="AJ59:AL59"/>
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="AS26:AU26"/>
+    <mergeCell ref="AE65:AF65"/>
     <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="J27:P27"/>
     <mergeCell ref="AG25:AI25"/>
     <mergeCell ref="AY33:BA33"/>
-    <mergeCell ref="A52:BQ52"/>
     <mergeCell ref="BB53:BD53"/>
     <mergeCell ref="T5:AH5"/>
     <mergeCell ref="AM22:AO22"/>
     <mergeCell ref="AP23:AR23"/>
     <mergeCell ref="B56:D56"/>
     <mergeCell ref="J20:P20"/>
+    <mergeCell ref="AJ61:AL61"/>
     <mergeCell ref="AV47:AX47"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="BE51:BG51"/>
     <mergeCell ref="AY50:BA50"/>
-    <mergeCell ref="BB55:BD55"/>
     <mergeCell ref="BK33:BQ33"/>
     <mergeCell ref="A5:S5"/>
     <mergeCell ref="J22:P22"/>
+    <mergeCell ref="BH62:BJ62"/>
     <mergeCell ref="AV38:AX38"/>
+    <mergeCell ref="AY52:BA52"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="AY39:BA39"/>
+    <mergeCell ref="AS52:AU52"/>
     <mergeCell ref="AG53:AI53"/>
     <mergeCell ref="X44:AD44"/>
     <mergeCell ref="AP34:AR34"/>
@@ -15003,6 +16355,7 @@
     <mergeCell ref="BH57:BJ57"/>
     <mergeCell ref="AG13:AI13"/>
     <mergeCell ref="AV33:AX33"/>
+    <mergeCell ref="BE61:BG61"/>
     <mergeCell ref="AP36:AR36"/>
     <mergeCell ref="AS37:AU37"/>
     <mergeCell ref="AE14:AF14"/>
@@ -15016,12 +16369,16 @@
     <mergeCell ref="AJ16:AL16"/>
     <mergeCell ref="X32:AD32"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="A55:BQ55"/>
     <mergeCell ref="E59:I59"/>
     <mergeCell ref="E46:I46"/>
     <mergeCell ref="J40:P40"/>
+    <mergeCell ref="BE62:BG62"/>
     <mergeCell ref="J15:P15"/>
+    <mergeCell ref="AY65:BA65"/>
     <mergeCell ref="AM41:AO41"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="E61:I61"/>
     <mergeCell ref="A29:BQ29"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
@@ -15029,7 +16386,9 @@
     <mergeCell ref="E54:I54"/>
     <mergeCell ref="AV22:AX22"/>
     <mergeCell ref="AY23:BA23"/>
+    <mergeCell ref="AS63:AU63"/>
     <mergeCell ref="E41:I41"/>
+    <mergeCell ref="X65:AD65"/>
     <mergeCell ref="AE27:AF27"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
@@ -15037,6 +16396,7 @@
     <mergeCell ref="E56:I56"/>
     <mergeCell ref="AV51:AX51"/>
     <mergeCell ref="E43:I43"/>
+    <mergeCell ref="X63:AD63"/>
     <mergeCell ref="BB15:BD15"/>
     <mergeCell ref="BE16:BG16"/>
     <mergeCell ref="AE20:AF20"/>
@@ -15044,10 +16404,12 @@
     <mergeCell ref="AE25:AF25"/>
     <mergeCell ref="AS40:AU40"/>
     <mergeCell ref="X50:AD50"/>
+    <mergeCell ref="BH52:BJ52"/>
     <mergeCell ref="AS27:AU27"/>
     <mergeCell ref="AP31:AR31"/>
     <mergeCell ref="BH14:BJ14"/>
     <mergeCell ref="BK54:BQ54"/>
+    <mergeCell ref="AJ62:AL62"/>
     <mergeCell ref="AJ37:AL37"/>
     <mergeCell ref="AY49:BA49"/>
     <mergeCell ref="BE11:BG11"/>
@@ -15056,12 +16418,15 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="Q16:W16"/>
     <mergeCell ref="AV40:AX40"/>
+    <mergeCell ref="B65:D65"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="J28:P28"/>
+    <mergeCell ref="X52:AD52"/>
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="AG30:AI30"/>
     <mergeCell ref="Q18:W18"/>
     <mergeCell ref="BK49:BQ49"/>
+    <mergeCell ref="B63:D63"/>
     <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AE38:AF38"/>
     <mergeCell ref="AV54:AX54"/>
@@ -15080,11 +16445,13 @@
     <mergeCell ref="AM14:AO14"/>
     <mergeCell ref="AE15:AF15"/>
     <mergeCell ref="AP42:AR42"/>
+    <mergeCell ref="BH63:BJ63"/>
     <mergeCell ref="AJ42:AL42"/>
     <mergeCell ref="AP58:AR58"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="AM13:AO13"/>
-    <mergeCell ref="X55:AD55"/>
+    <mergeCell ref="AP52:AR52"/>
+    <mergeCell ref="AM62:AO62"/>
     <mergeCell ref="AJ17:AL17"/>
     <mergeCell ref="AM56:AO56"/>
     <mergeCell ref="J54:P54"/>
@@ -15093,6 +16460,7 @@
     <mergeCell ref="Q44:W44"/>
     <mergeCell ref="AV43:AX43"/>
     <mergeCell ref="AJ19:AL19"/>
+    <mergeCell ref="E62:I62"/>
     <mergeCell ref="J56:P56"/>
     <mergeCell ref="AY58:BA58"/>
     <mergeCell ref="J43:P43"/>
@@ -15103,9 +16471,9 @@
     <mergeCell ref="BK31:BQ31"/>
     <mergeCell ref="AG18:AI18"/>
     <mergeCell ref="BE17:BG17"/>
-    <mergeCell ref="B55:D55"/>
     <mergeCell ref="AM25:AO25"/>
     <mergeCell ref="N6:P6"/>
+    <mergeCell ref="E65:I65"/>
     <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
@@ -15123,22 +16491,25 @@
     <mergeCell ref="Q26:W26"/>
     <mergeCell ref="AG10:AU10"/>
     <mergeCell ref="AG44:AI44"/>
+    <mergeCell ref="AV62:AX62"/>
     <mergeCell ref="BE14:BG14"/>
     <mergeCell ref="BB24:BD24"/>
     <mergeCell ref="AM28:AO28"/>
     <mergeCell ref="BB18:BD18"/>
     <mergeCell ref="AG31:AI31"/>
+    <mergeCell ref="B52:D52"/>
     <mergeCell ref="AV56:AX56"/>
     <mergeCell ref="B58:D58"/>
+    <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE20 AE22:AE28 AE30:AE34 AE36:AE51 AE53:AE59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE20 AE22:AE28 AE30:AE34 AE36:AE54 AE56:AE63 AE65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG20 AG22:AG28 AG30:AG34 AG36:AG51 AG53:AG59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG20 AG22:AG28 AG30:AG34 AG36:AG54 AG56:AG63 AG65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV20 AV22:AV28 AV30:AV34 AV36:AV51 AV53:AV59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV20 AV22:AV28 AV30:AV34 AV36:AV54 AV56:AV63 AV65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/docs/design/ACSMS-SCR-029/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_増減通知（日本農業新聞）出力画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-029/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_増減通知（日本農業新聞）出力画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH4"/>
+  <dimension ref="A1:AH5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1475,16 +1475,73 @@
       <c r="AG4" s="10" t="n"/>
       <c r="AH4" s="11" t="n"/>
     </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="18" t="inlineStr"/>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="11" t="n"/>
+      <c r="I5" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="n"/>
+      <c r="K5" s="10" t="n"/>
+      <c r="L5" s="10" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="11" t="n"/>
+      <c r="O5" s="20" t="inlineStr">
+        <is>
+          <t>顧客報告 #57976 の不具合修正に伴い TC-029-028 を書き換え：本帳票は廃店(haiten_flg)を除外しない（SCR-028とは方針が異なる）ことを確認する内容に変更。電子版ダミー販売店は従来どおり紙版限定フィルタで対象外（API設計書 v1.6）。</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="10" t="n"/>
+      <c r="R5" s="10" t="n"/>
+      <c r="S5" s="10" t="n"/>
+      <c r="T5" s="10" t="n"/>
+      <c r="U5" s="10" t="n"/>
+      <c r="V5" s="11" t="n"/>
+      <c r="W5" s="19" t="inlineStr"/>
+      <c r="X5" s="10" t="n"/>
+      <c r="Y5" s="10" t="n"/>
+      <c r="Z5" s="10" t="n"/>
+      <c r="AA5" s="10" t="n"/>
+      <c r="AB5" s="11" t="n"/>
+      <c r="AC5" s="19" t="inlineStr"/>
+      <c r="AD5" s="10" t="n"/>
+      <c r="AE5" s="10" t="n"/>
+      <c r="AF5" s="10" t="n"/>
+      <c r="AG5" s="10" t="n"/>
+      <c r="AH5" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="30">
     <mergeCell ref="O3:V3"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="AC5:AH5"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="W3:AB3"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I3:N3"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="AC4:AH4"/>
     <mergeCell ref="AC1:AH1"/>
     <mergeCell ref="B4:E4"/>
+    <mergeCell ref="I5:N5"/>
+    <mergeCell ref="O5:V5"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="B3:E3"/>
@@ -1499,6 +1556,7 @@
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
+    <mergeCell ref="W5:AB5"/>
     <mergeCell ref="AC3:AH3"/>
     <mergeCell ref="F3:H3"/>
   </mergeCells>
@@ -12292,7 +12350,7 @@
       <c r="BP45" s="10" t="n"/>
       <c r="BQ45" s="11" t="n"/>
     </row>
-    <row r="46" ht="64" customHeight="1">
+    <row r="46" ht="272" customHeight="1">
       <c r="A46" s="44" t="n">
         <v>31</v>
       </c>
@@ -12305,7 +12363,7 @@
       <c r="D46" s="11" t="n"/>
       <c r="E46" s="46" t="inlineStr">
         <is>
-          <t>廃店の除外</t>
+          <t>廃店は除外しない・電子版ダミー販売店は除外する（#57976）</t>
         </is>
       </c>
       <c r="F46" s="10" t="n"/>
@@ -12315,7 +12373,8 @@
       <c r="J46" s="46" t="inlineStr">
         <is>
           <t>・CHUOKAI でログイン済み
-・廃店（haiten_flg=true）・電子版ダミー販売店の履歴が存在する</t>
+・廃店（haiten_flg=true）に紐づく紙版購読者の履歴（zougen_hokoku_flg=true）が存在する
+・電子版ダミー販売店（hanbaiten_code=9999999999）に紐づく履歴が存在する</t>
         </is>
       </c>
       <c r="K46" s="10" t="n"/>
@@ -12366,7 +12425,39 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>廃店（haiten_flg=true）・電子版ダミー販売店に紐づくレコードが表示されないこと</t>
+            <t xml:space="preserve">廃店（haiten_flg=true）に紐づくレコードは**表示されること**——本帳票は日本農業新聞への
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">増減通知であり、特定の販売店を報告の宛先にするものではないため、販売店の営業状態に
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">関係なく増減を通知する必要がある（SCR-028 増減連絡票（販売店）とは異なる方針）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">電子版ダミー販売店に紐づくレコードは表示されないこと——`dokusya_shubetsu = 1`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>（紙版のみ集計）により、電子版専用のダミー販売店に紐づく購読者は元々対象外となる</t>
           </r>
         </is>
       </c>
@@ -15544,7 +15635,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・本画面は出力条件に販売店の入力欄が無いため、ダミー販売店の表示制御（#56597）は対象外。ただし集計SQL側では `h.haiten_flg = false` により廃店・ダミー販売店を除外している
+            <t xml:space="preserve">・本画面は出力条件に販売店の入力欄が無いため、ダミー販売店の表示制御（#56597）は対象外。ダミー販売店に紐づくのは電子版購読者のみであり、`dokusya_shubetsu = 1`（紙版のみ集計）により対象外となる。廃店（`haiten_flg`）は除外しない（#57976・ACSMS-TC-029-028 参照）
 </t>
           </r>
           <r>
